--- a/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/20261029_管理手順書_5-7章_デザイン適用/管理手順書_5-7章_デザイン適用_20261029.xlsx
+++ b/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/20261029_管理手順書_5-7章_デザイン適用/管理手順書_5-7章_デザイン適用_20261029.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ss80751\AppData\Local\Temp\kohden-code\issue6263_work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63AF44D7-60F9-4D91-9D95-C5CE6ECD59CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52342445-B23D-44EE-94C8-4024641C56C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{F138DDEF-1479-478C-A631-F11C3677646E}"/>
   </bookViews>
@@ -1251,7 +1251,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1330,16 +1330,22 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1352,12 +1358,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1748,7 +1748,7 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>99136</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:rowOff>36576</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1765,8 +1765,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="198196" y="14196060"/>
-          <a:ext cx="762000" cy="304800"/>
+          <a:off x="190576" y="19095720"/>
+          <a:ext cx="762000" cy="280416"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartTerminator">
           <a:avLst/>
@@ -1825,14 +1825,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>68656</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>27940</xdr:rowOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>153416</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>59055</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>55880</xdr:rowOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>140716</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1849,8 +1849,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="198196" y="14627860"/>
-          <a:ext cx="1453439" cy="508000"/>
+          <a:off x="190576" y="19492976"/>
+          <a:ext cx="1453439" cy="467360"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
@@ -1913,14 +1913,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>68656</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>10160</xdr:rowOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>85852</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>59055</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>73152</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1937,8 +1937,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="198196" y="15250160"/>
-          <a:ext cx="1453439" cy="508000"/>
+          <a:off x="190576" y="20065492"/>
+          <a:ext cx="1453439" cy="467360"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
@@ -2002,13 +2002,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>68656</xdr:colOff>
       <xdr:row>82</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:rowOff>18287</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>59055</xdr:colOff>
       <xdr:row>85</xdr:row>
-      <xdr:rowOff>180340</xdr:rowOff>
+      <xdr:rowOff>5587</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2025,8 +2025,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="198196" y="15872460"/>
-          <a:ext cx="1453439" cy="508000"/>
+          <a:off x="190576" y="20638007"/>
+          <a:ext cx="1453439" cy="467360"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
@@ -2107,14 +2107,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>68656</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>111760</xdr:rowOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>110744</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>59055</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>75184</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2131,8 +2131,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="198196" y="16494760"/>
-          <a:ext cx="1453439" cy="508000"/>
+          <a:off x="190576" y="21210524"/>
+          <a:ext cx="1453439" cy="467360"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
@@ -2195,14 +2195,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>68656</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>93980</xdr:rowOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>20319</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>59055</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>7619</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2219,8 +2219,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="198196" y="17117060"/>
-          <a:ext cx="1453439" cy="508000"/>
+          <a:off x="190576" y="21783039"/>
+          <a:ext cx="1453439" cy="467360"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
@@ -2301,14 +2301,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>68656</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>112776</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>59055</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>104140</xdr:rowOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>100076</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2325,8 +2325,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="198196" y="17739360"/>
-          <a:ext cx="1453439" cy="508000"/>
+          <a:off x="190576" y="22355556"/>
+          <a:ext cx="1453439" cy="467360"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
@@ -2390,13 +2390,13 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>18136</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:rowOff>36575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>18136</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>27940</xdr:rowOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>153415</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2413,8 +2413,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="924916" y="14500860"/>
-          <a:ext cx="0" cy="127000"/>
+          <a:off x="871576" y="19376135"/>
+          <a:ext cx="0" cy="116840"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2447,14 +2447,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>18136</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>55880</xdr:rowOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>140715</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>18136</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>10160</xdr:rowOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>85851</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2471,8 +2471,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="924916" y="15135860"/>
-          <a:ext cx="0" cy="114300"/>
+          <a:off x="871576" y="19960335"/>
+          <a:ext cx="0" cy="105156"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2505,14 +2505,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>18136</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>73152</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>18136</xdr:colOff>
       <xdr:row>82</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:rowOff>18288</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2529,8 +2529,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="924916" y="15758160"/>
-          <a:ext cx="0" cy="114300"/>
+          <a:off x="871576" y="20532852"/>
+          <a:ext cx="0" cy="105156"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2564,13 +2564,13 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>18136</xdr:colOff>
       <xdr:row>85</xdr:row>
-      <xdr:rowOff>180340</xdr:rowOff>
+      <xdr:rowOff>5588</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>18136</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>111760</xdr:rowOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>110744</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2587,8 +2587,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="924916" y="16380460"/>
-          <a:ext cx="0" cy="114300"/>
+          <a:off x="871576" y="21105368"/>
+          <a:ext cx="0" cy="105156"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2621,14 +2621,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>18136</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>75183</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>18136</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>93980</xdr:rowOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>20319</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2645,8 +2645,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="924916" y="17002760"/>
-          <a:ext cx="0" cy="114300"/>
+          <a:off x="871576" y="21677883"/>
+          <a:ext cx="0" cy="105156"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2679,14 +2679,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>18136</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>18136</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>112776</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2703,8 +2703,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="924916" y="17625060"/>
-          <a:ext cx="0" cy="114300"/>
+          <a:off x="871576" y="22250400"/>
+          <a:ext cx="0" cy="105156"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2737,14 +2737,14 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>97156</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>10160</xdr:rowOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>26415</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>28703</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>10160</xdr:rowOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>26415</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2761,7 +2761,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1651636" y="17993360"/>
+          <a:off x="1560196" y="22589235"/>
           <a:ext cx="297307" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -2795,13 +2795,13 @@
       <xdr:col>15</xdr:col>
       <xdr:colOff>5842</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:rowOff>36575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>5842</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>10160</xdr:rowOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>26415</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2818,8 +2818,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="1948942" y="14500860"/>
-          <a:ext cx="0" cy="3492500"/>
+          <a:off x="1834642" y="19376135"/>
+          <a:ext cx="0" cy="3213100"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2852,13 +2852,13 @@
       <xdr:col>17</xdr:col>
       <xdr:colOff>44044</xdr:colOff>
       <xdr:row>72</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:rowOff>122936</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>34443</xdr:colOff>
       <xdr:row>75</xdr:row>
-      <xdr:rowOff>154940</xdr:rowOff>
+      <xdr:rowOff>110236</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2875,8 +2875,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2246224" y="14246860"/>
-          <a:ext cx="1453439" cy="508000"/>
+          <a:off x="2116684" y="19142456"/>
+          <a:ext cx="1453439" cy="467360"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
@@ -2958,13 +2958,13 @@
       <xdr:col>17</xdr:col>
       <xdr:colOff>44044</xdr:colOff>
       <xdr:row>76</xdr:row>
-      <xdr:rowOff>109220</xdr:rowOff>
+      <xdr:rowOff>55372</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>34443</xdr:colOff>
       <xdr:row>79</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
+      <xdr:rowOff>42672</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2981,8 +2981,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2246224" y="14869160"/>
-          <a:ext cx="1453439" cy="508000"/>
+          <a:off x="2116684" y="19714972"/>
+          <a:ext cx="1453439" cy="467360"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
@@ -3045,14 +3045,14 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>44044</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>147827</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>34443</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>119380</xdr:rowOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>135127</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3069,8 +3069,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2246224" y="15491460"/>
-          <a:ext cx="1453439" cy="508000"/>
+          <a:off x="2116684" y="20287487"/>
+          <a:ext cx="1453439" cy="467360"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
@@ -3130,14 +3130,14 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>44044</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>73660</xdr:rowOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>80264</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>34443</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>78740</xdr:rowOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>44704</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3154,8 +3154,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2246224" y="16113760"/>
-          <a:ext cx="1453439" cy="508000"/>
+          <a:off x="2116684" y="20860004"/>
+          <a:ext cx="1453439" cy="467360"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
@@ -3218,14 +3218,14 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>44044</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>33020</xdr:rowOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>149860</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>34443</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3242,8 +3242,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2246224" y="16736060"/>
-          <a:ext cx="1453439" cy="508000"/>
+          <a:off x="2116684" y="21432520"/>
+          <a:ext cx="1453439" cy="467360"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
@@ -3306,14 +3306,14 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>44044</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>82295</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>34443</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>43180</xdr:rowOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>69595</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3330,8 +3330,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2246224" y="17358360"/>
-          <a:ext cx="1453439" cy="508000"/>
+          <a:off x="2116684" y="22005035"/>
+          <a:ext cx="1453439" cy="467360"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
@@ -3394,14 +3394,14 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>44044</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>157480</xdr:rowOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>14732</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>34443</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>2032</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3418,8 +3418,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2246224" y="17980660"/>
-          <a:ext cx="1453439" cy="508000"/>
+          <a:off x="2116684" y="22577552"/>
+          <a:ext cx="1453439" cy="467360"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
@@ -3480,16 +3480,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>123063</xdr:colOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1143</xdr:colOff>
       <xdr:row>75</xdr:row>
-      <xdr:rowOff>154940</xdr:rowOff>
+      <xdr:rowOff>110235</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>1143</xdr:colOff>
       <xdr:row>76</xdr:row>
-      <xdr:rowOff>109220</xdr:rowOff>
+      <xdr:rowOff>55371</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3506,8 +3506,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2972943" y="14754860"/>
-          <a:ext cx="0" cy="114300"/>
+          <a:off x="2805303" y="19609815"/>
+          <a:ext cx="0" cy="105156"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3538,16 +3538,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>123063</xdr:colOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1143</xdr:colOff>
       <xdr:row>79</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
+      <xdr:rowOff>42672</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>1143</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>147828</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3564,8 +3564,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2972943" y="15377160"/>
-          <a:ext cx="0" cy="114300"/>
+          <a:off x="2805303" y="20182332"/>
+          <a:ext cx="0" cy="105156"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3596,16 +3596,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>123063</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>119380</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1143</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>135128</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>1143</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>73660</xdr:rowOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>80264</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3622,8 +3622,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2972943" y="15999460"/>
-          <a:ext cx="0" cy="114300"/>
+          <a:off x="2805303" y="20754848"/>
+          <a:ext cx="0" cy="105156"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3654,16 +3654,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>123063</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>78740</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1143</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>44703</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>1143</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>33020</xdr:rowOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>149859</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3680,8 +3680,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2972943" y="16621760"/>
-          <a:ext cx="0" cy="114300"/>
+          <a:off x="2805303" y="21327363"/>
+          <a:ext cx="0" cy="105156"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3712,16 +3712,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>123063</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1143</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>1143</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>82296</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3738,8 +3738,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2972943" y="17244060"/>
-          <a:ext cx="0" cy="114300"/>
+          <a:off x="2805303" y="21899880"/>
+          <a:ext cx="0" cy="105156"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3770,16 +3770,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>123063</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>43180</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1143</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>69596</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>1143</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>157480</xdr:rowOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>14732</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3796,8 +3796,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2972943" y="17866360"/>
-          <a:ext cx="0" cy="114300"/>
+          <a:off x="2805303" y="22472396"/>
+          <a:ext cx="0" cy="105156"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3830,14 +3830,14 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>6438</xdr:colOff>
-      <xdr:row>100</xdr:row>
-      <xdr:rowOff>17780</xdr:rowOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>142240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>30</xdr:col>
       <xdr:colOff>87288</xdr:colOff>
-      <xdr:row>104</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>109728</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3854,8 +3854,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2079078" y="18641060"/>
-          <a:ext cx="1787730" cy="660400"/>
+          <a:off x="1957158" y="23185120"/>
+          <a:ext cx="1787730" cy="607568"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartDecision">
           <a:avLst/>
@@ -3905,14 +3905,14 @@
     <xdr:from>
       <xdr:col>18</xdr:col>
       <xdr:colOff>57023</xdr:colOff>
-      <xdr:row>100</xdr:row>
-      <xdr:rowOff>157481</xdr:rowOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>93929</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>6223</xdr:colOff>
-      <xdr:row>103</xdr:row>
-      <xdr:rowOff>58421</xdr:rowOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>4953</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>34239</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3929,8 +3929,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2388743" y="18780761"/>
-          <a:ext cx="1168400" cy="381000"/>
+          <a:off x="2251583" y="23296829"/>
+          <a:ext cx="1289050" cy="420370"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4008,14 +4008,14 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>44044</xdr:colOff>
-      <xdr:row>105</xdr:row>
-      <xdr:rowOff>81280</xdr:rowOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>136652</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>34443</xdr:colOff>
-      <xdr:row>108</xdr:row>
-      <xdr:rowOff>109220</xdr:rowOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>123952</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4032,8 +4032,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2246224" y="19504660"/>
-          <a:ext cx="1453439" cy="508000"/>
+          <a:off x="2116684" y="23979632"/>
+          <a:ext cx="1453439" cy="467360"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
@@ -4114,14 +4114,14 @@
     <xdr:from>
       <xdr:col>18</xdr:col>
       <xdr:colOff>6223</xdr:colOff>
-      <xdr:row>109</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>127508</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
       <xdr:colOff>57023</xdr:colOff>
-      <xdr:row>112</xdr:row>
-      <xdr:rowOff>27940</xdr:rowOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>157988</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4138,8 +4138,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2337943" y="20190460"/>
-          <a:ext cx="1270000" cy="381000"/>
+          <a:off x="2200783" y="24610568"/>
+          <a:ext cx="1270000" cy="350520"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartTerminator">
           <a:avLst/>
@@ -4196,16 +4196,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>123063</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1143</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>2031</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>1143</xdr:colOff>
-      <xdr:row>100</xdr:row>
-      <xdr:rowOff>17780</xdr:rowOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>142239</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -4222,8 +4222,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2972943" y="18488660"/>
-          <a:ext cx="0" cy="152400"/>
+          <a:off x="2805303" y="23044911"/>
+          <a:ext cx="0" cy="140208"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -4254,16 +4254,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>123063</xdr:colOff>
-      <xdr:row>104</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1143</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>109727</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>1143</xdr:colOff>
-      <xdr:row>105</xdr:row>
-      <xdr:rowOff>81280</xdr:rowOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>136651</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -4280,8 +4280,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2972943" y="19301460"/>
-          <a:ext cx="0" cy="203200"/>
+          <a:off x="2805303" y="23792687"/>
+          <a:ext cx="0" cy="186944"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -4312,16 +4312,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>123063</xdr:colOff>
-      <xdr:row>108</xdr:row>
-      <xdr:rowOff>109220</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>1143</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>123952</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>1143</xdr:colOff>
-      <xdr:row>109</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>127508</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -4338,8 +4338,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2972943" y="20012660"/>
-          <a:ext cx="0" cy="177800"/>
+          <a:off x="2805303" y="24446992"/>
+          <a:ext cx="0" cy="163576"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -4372,14 +4372,14 @@
     <xdr:from>
       <xdr:col>32</xdr:col>
       <xdr:colOff>26328</xdr:colOff>
-      <xdr:row>100</xdr:row>
-      <xdr:rowOff>93980</xdr:rowOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>52324</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>39</xdr:col>
       <xdr:colOff>64771</xdr:colOff>
-      <xdr:row>103</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>39624</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4396,8 +4396,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4171608" y="18717260"/>
-          <a:ext cx="891883" cy="508000"/>
+          <a:off x="3927768" y="23255224"/>
+          <a:ext cx="891883" cy="467360"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
@@ -4469,14 +4469,14 @@
     <xdr:from>
       <xdr:col>29</xdr:col>
       <xdr:colOff>110148</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>27940</xdr:rowOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>125984</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
       <xdr:colOff>49188</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>27940</xdr:rowOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>125984</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -4493,7 +4493,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3866808" y="18971260"/>
+          <a:off x="3645828" y="23488904"/>
           <a:ext cx="304800" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -4527,14 +4527,14 @@
     <xdr:from>
       <xdr:col>35</xdr:col>
       <xdr:colOff>83649</xdr:colOff>
-      <xdr:row>103</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>39623</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>35</xdr:col>
       <xdr:colOff>83649</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>50291</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -4551,8 +4551,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4617549" y="19225260"/>
-          <a:ext cx="0" cy="533400"/>
+          <a:off x="4350849" y="23722583"/>
+          <a:ext cx="0" cy="490728"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -4582,16 +4582,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>122848</xdr:colOff>
-      <xdr:row>100</xdr:row>
-      <xdr:rowOff>132080</xdr:rowOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>928</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>80263</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
       <xdr:colOff>36488</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>149860</xdr:rowOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>98043</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4608,7 +4608,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3879508" y="18755360"/>
+          <a:off x="3658528" y="23283163"/>
           <a:ext cx="279400" cy="177800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4674,14 +4674,14 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>25273</xdr:colOff>
-      <xdr:row>104</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>96393</xdr:colOff>
-      <xdr:row>105</xdr:row>
-      <xdr:rowOff>68580</xdr:rowOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>132081</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4698,7 +4698,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3004693" y="19314160"/>
+          <a:off x="2829433" y="23797261"/>
           <a:ext cx="558800" cy="177800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4764,14 +4764,14 @@
     <xdr:from>
       <xdr:col>28</xdr:col>
       <xdr:colOff>72543</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>50291</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>36</xdr:col>
       <xdr:colOff>15070</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>50291</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -4788,7 +4788,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="3699663" y="19758660"/>
+          <a:off x="3486303" y="24213311"/>
           <a:ext cx="917887" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -4824,13 +4824,13 @@
       <xdr:col>15</xdr:col>
       <xdr:colOff>5842</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:rowOff>36575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>59309</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:rowOff>36575</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -4847,7 +4847,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1948942" y="14500860"/>
+          <a:off x="1834642" y="19376135"/>
           <a:ext cx="297307" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -6194,7 +6194,7 @@
       <c r="C8" s="9"/>
     </row>
     <row r="9" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="63" t="s">
         <v>65</v>
       </c>
       <c r="D9" s="33"/>
@@ -7819,7 +7819,7 @@
       <c r="AZ183" s="41"/>
     </row>
     <row r="184" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C184" s="71" t="s">
+      <c r="C184" s="32" t="s">
         <v>89</v>
       </c>
       <c r="D184" s="33"/>
@@ -7873,7 +7873,7 @@
       <c r="AZ184" s="33"/>
     </row>
     <row r="185" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C185" s="71" t="s">
+      <c r="C185" s="32" t="s">
         <v>90</v>
       </c>
       <c r="D185" s="33"/>
@@ -7927,7 +7927,7 @@
       <c r="AZ185" s="33"/>
     </row>
     <row r="186" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C186" s="71" t="s">
+      <c r="C186" s="32" t="s">
         <v>91</v>
       </c>
       <c r="D186" s="33"/>
@@ -7981,7 +7981,7 @@
       <c r="AZ186" s="33"/>
     </row>
     <row r="187" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C187" s="71" t="s">
+      <c r="C187" s="32" t="s">
         <v>92</v>
       </c>
       <c r="D187" s="33"/>
@@ -8035,7 +8035,7 @@
       <c r="AZ187" s="33"/>
     </row>
     <row r="188" spans="1:52" ht="49.05" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C188" s="71" t="s">
+      <c r="C188" s="32" t="s">
         <v>93</v>
       </c>
       <c r="D188" s="33"/>
@@ -8478,7 +8478,7 @@
       <c r="AZ6" s="39"/>
     </row>
     <row r="7" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C7" s="71" t="s">
+      <c r="C7" s="32" t="s">
         <v>94</v>
       </c>
       <c r="D7" s="33"/>
@@ -8532,7 +8532,7 @@
       <c r="AZ7" s="33"/>
     </row>
     <row r="8" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C8" s="71" t="s">
+      <c r="C8" s="32" t="s">
         <v>95</v>
       </c>
       <c r="D8" s="33"/>
@@ -8586,7 +8586,7 @@
       <c r="AZ8" s="33"/>
     </row>
     <row r="9" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C9" s="71" t="s">
+      <c r="C9" s="32" t="s">
         <v>96</v>
       </c>
       <c r="D9" s="33"/>
@@ -8640,7 +8640,7 @@
       <c r="AZ9" s="33"/>
     </row>
     <row r="10" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C10" s="71" t="s">
+      <c r="C10" s="32" t="s">
         <v>97</v>
       </c>
       <c r="D10" s="33"/>
@@ -8694,58 +8694,58 @@
       <c r="AZ10" s="33"/>
     </row>
     <row r="11" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C11" s="72" t="s">
+      <c r="C11" s="64" t="s">
         <v>98</v>
       </c>
-      <c r="D11" s="63"/>
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63"/>
-      <c r="I11" s="63"/>
-      <c r="J11" s="63"/>
-      <c r="K11" s="63"/>
-      <c r="L11" s="63"/>
-      <c r="M11" s="63"/>
-      <c r="N11" s="63"/>
-      <c r="O11" s="63"/>
-      <c r="P11" s="63"/>
-      <c r="Q11" s="63"/>
-      <c r="R11" s="63"/>
-      <c r="S11" s="63"/>
-      <c r="T11" s="63"/>
-      <c r="U11" s="63"/>
-      <c r="V11" s="63"/>
-      <c r="W11" s="63"/>
-      <c r="X11" s="63"/>
-      <c r="Y11" s="63"/>
-      <c r="Z11" s="63"/>
-      <c r="AA11" s="63"/>
-      <c r="AB11" s="63"/>
-      <c r="AC11" s="63"/>
-      <c r="AD11" s="63"/>
-      <c r="AE11" s="63"/>
-      <c r="AF11" s="63"/>
-      <c r="AG11" s="63"/>
-      <c r="AH11" s="63"/>
-      <c r="AI11" s="63"/>
-      <c r="AJ11" s="63"/>
-      <c r="AK11" s="63"/>
-      <c r="AL11" s="63"/>
-      <c r="AM11" s="63"/>
-      <c r="AN11" s="63"/>
-      <c r="AO11" s="63"/>
-      <c r="AP11" s="63"/>
-      <c r="AQ11" s="63"/>
-      <c r="AR11" s="63"/>
-      <c r="AS11" s="63"/>
-      <c r="AT11" s="63"/>
-      <c r="AU11" s="63"/>
-      <c r="AV11" s="63"/>
-      <c r="AW11" s="63"/>
-      <c r="AX11" s="63"/>
-      <c r="AY11" s="63"/>
-      <c r="AZ11" s="63"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="65"/>
+      <c r="L11" s="65"/>
+      <c r="M11" s="65"/>
+      <c r="N11" s="65"/>
+      <c r="O11" s="65"/>
+      <c r="P11" s="65"/>
+      <c r="Q11" s="65"/>
+      <c r="R11" s="65"/>
+      <c r="S11" s="65"/>
+      <c r="T11" s="65"/>
+      <c r="U11" s="65"/>
+      <c r="V11" s="65"/>
+      <c r="W11" s="65"/>
+      <c r="X11" s="65"/>
+      <c r="Y11" s="65"/>
+      <c r="Z11" s="65"/>
+      <c r="AA11" s="65"/>
+      <c r="AB11" s="65"/>
+      <c r="AC11" s="65"/>
+      <c r="AD11" s="65"/>
+      <c r="AE11" s="65"/>
+      <c r="AF11" s="65"/>
+      <c r="AG11" s="65"/>
+      <c r="AH11" s="65"/>
+      <c r="AI11" s="65"/>
+      <c r="AJ11" s="65"/>
+      <c r="AK11" s="65"/>
+      <c r="AL11" s="65"/>
+      <c r="AM11" s="65"/>
+      <c r="AN11" s="65"/>
+      <c r="AO11" s="65"/>
+      <c r="AP11" s="65"/>
+      <c r="AQ11" s="65"/>
+      <c r="AR11" s="65"/>
+      <c r="AS11" s="65"/>
+      <c r="AT11" s="65"/>
+      <c r="AU11" s="65"/>
+      <c r="AV11" s="65"/>
+      <c r="AW11" s="65"/>
+      <c r="AX11" s="65"/>
+      <c r="AY11" s="65"/>
+      <c r="AZ11" s="65"/>
     </row>
     <row r="13" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C13" s="34" t="s">
@@ -9495,7 +9495,7 @@
       <c r="AZ6" s="39"/>
     </row>
     <row r="7" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C7" s="71" t="s">
+      <c r="C7" s="32" t="s">
         <v>99</v>
       </c>
       <c r="D7" s="33"/>
@@ -9603,7 +9603,7 @@
       <c r="AZ8" s="62"/>
     </row>
     <row r="9" spans="1:52" ht="49.05" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C9" s="71" t="s">
+      <c r="C9" s="32" t="s">
         <v>101</v>
       </c>
       <c r="D9" s="33"/>
@@ -9822,7 +9822,7 @@
       <c r="AZ13" s="62"/>
     </row>
     <row r="14" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C14" s="71" t="s">
+      <c r="C14" s="32" t="s">
         <v>104</v>
       </c>
       <c r="D14" s="33"/>
@@ -9876,7 +9876,7 @@
       <c r="AZ14" s="33"/>
     </row>
     <row r="15" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C15" s="71" t="s">
+      <c r="C15" s="32" t="s">
         <v>105</v>
       </c>
       <c r="D15" s="33"/>
@@ -9930,7 +9930,7 @@
       <c r="AZ15" s="33"/>
     </row>
     <row r="16" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C16" s="71" t="s">
+      <c r="C16" s="32" t="s">
         <v>106</v>
       </c>
       <c r="D16" s="33"/>
@@ -9984,7 +9984,7 @@
       <c r="AZ16" s="33"/>
     </row>
     <row r="17" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C17" s="71" t="s">
+      <c r="C17" s="32" t="s">
         <v>107</v>
       </c>
       <c r="D17" s="33"/>
@@ -10038,7 +10038,7 @@
       <c r="AZ17" s="33"/>
     </row>
     <row r="18" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C18" s="71" t="s">
+      <c r="C18" s="32" t="s">
         <v>108</v>
       </c>
       <c r="D18" s="33"/>
@@ -10092,7 +10092,7 @@
       <c r="AZ18" s="33"/>
     </row>
     <row r="20" spans="1:52" ht="49.05" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="63" t="s">
         <v>10</v>
       </c>
       <c r="D20" s="33"/>
@@ -10254,7 +10254,7 @@
       <c r="AZ22" s="39"/>
     </row>
     <row r="23" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C23" s="71" t="s">
+      <c r="C23" s="32" t="s">
         <v>109</v>
       </c>
       <c r="D23" s="33"/>
@@ -10308,7 +10308,7 @@
       <c r="AZ23" s="33"/>
     </row>
     <row r="24" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C24" s="71" t="s">
+      <c r="C24" s="32" t="s">
         <v>110</v>
       </c>
       <c r="D24" s="33"/>
@@ -10363,7 +10363,7 @@
     </row>
     <row r="25" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10"/>
-      <c r="C25" s="71" t="s">
+      <c r="C25" s="32" t="s">
         <v>111</v>
       </c>
       <c r="D25" s="33"/>
@@ -10532,55 +10532,55 @@
       <c r="C29" s="66" t="s">
         <v>112</v>
       </c>
-      <c r="D29" s="65"/>
-      <c r="E29" s="65"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
-      <c r="H29" s="65"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="65"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="65"/>
-      <c r="M29" s="65"/>
-      <c r="N29" s="65"/>
-      <c r="O29" s="65"/>
-      <c r="P29" s="65"/>
-      <c r="Q29" s="65"/>
-      <c r="R29" s="65"/>
-      <c r="S29" s="65"/>
-      <c r="T29" s="65"/>
-      <c r="U29" s="65"/>
-      <c r="V29" s="65"/>
-      <c r="W29" s="65"/>
-      <c r="X29" s="65"/>
-      <c r="Y29" s="65"/>
-      <c r="Z29" s="65"/>
-      <c r="AA29" s="65"/>
-      <c r="AB29" s="65"/>
-      <c r="AC29" s="65"/>
-      <c r="AD29" s="65"/>
-      <c r="AE29" s="65"/>
-      <c r="AF29" s="65"/>
-      <c r="AG29" s="65"/>
-      <c r="AH29" s="65"/>
-      <c r="AI29" s="65"/>
-      <c r="AJ29" s="65"/>
-      <c r="AK29" s="65"/>
-      <c r="AL29" s="65"/>
-      <c r="AM29" s="65"/>
-      <c r="AN29" s="65"/>
-      <c r="AO29" s="65"/>
-      <c r="AP29" s="65"/>
-      <c r="AQ29" s="65"/>
-      <c r="AR29" s="65"/>
-      <c r="AS29" s="65"/>
-      <c r="AT29" s="65"/>
-      <c r="AU29" s="65"/>
-      <c r="AV29" s="65"/>
-      <c r="AW29" s="65"/>
-      <c r="AX29" s="65"/>
-      <c r="AY29" s="65"/>
-      <c r="AZ29" s="65"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="67"/>
+      <c r="F29" s="67"/>
+      <c r="G29" s="67"/>
+      <c r="H29" s="67"/>
+      <c r="I29" s="67"/>
+      <c r="J29" s="67"/>
+      <c r="K29" s="67"/>
+      <c r="L29" s="67"/>
+      <c r="M29" s="67"/>
+      <c r="N29" s="67"/>
+      <c r="O29" s="67"/>
+      <c r="P29" s="67"/>
+      <c r="Q29" s="67"/>
+      <c r="R29" s="67"/>
+      <c r="S29" s="67"/>
+      <c r="T29" s="67"/>
+      <c r="U29" s="67"/>
+      <c r="V29" s="67"/>
+      <c r="W29" s="67"/>
+      <c r="X29" s="67"/>
+      <c r="Y29" s="67"/>
+      <c r="Z29" s="67"/>
+      <c r="AA29" s="67"/>
+      <c r="AB29" s="67"/>
+      <c r="AC29" s="67"/>
+      <c r="AD29" s="67"/>
+      <c r="AE29" s="67"/>
+      <c r="AF29" s="67"/>
+      <c r="AG29" s="67"/>
+      <c r="AH29" s="67"/>
+      <c r="AI29" s="67"/>
+      <c r="AJ29" s="67"/>
+      <c r="AK29" s="67"/>
+      <c r="AL29" s="67"/>
+      <c r="AM29" s="67"/>
+      <c r="AN29" s="67"/>
+      <c r="AO29" s="67"/>
+      <c r="AP29" s="67"/>
+      <c r="AQ29" s="67"/>
+      <c r="AR29" s="67"/>
+      <c r="AS29" s="67"/>
+      <c r="AT29" s="67"/>
+      <c r="AU29" s="67"/>
+      <c r="AV29" s="67"/>
+      <c r="AW29" s="67"/>
+      <c r="AX29" s="67"/>
+      <c r="AY29" s="67"/>
+      <c r="AZ29" s="67"/>
     </row>
     <row r="30" spans="1:52" ht="49.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="11"/>
@@ -10588,55 +10588,55 @@
       <c r="C30" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="D30" s="65"/>
-      <c r="E30" s="65"/>
-      <c r="F30" s="65"/>
-      <c r="G30" s="65"/>
-      <c r="H30" s="65"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="65"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="65"/>
-      <c r="M30" s="65"/>
-      <c r="N30" s="65"/>
-      <c r="O30" s="65"/>
-      <c r="P30" s="65"/>
-      <c r="Q30" s="65"/>
-      <c r="R30" s="65"/>
-      <c r="S30" s="65"/>
-      <c r="T30" s="65"/>
-      <c r="U30" s="65"/>
-      <c r="V30" s="65"/>
-      <c r="W30" s="65"/>
-      <c r="X30" s="65"/>
-      <c r="Y30" s="65"/>
-      <c r="Z30" s="65"/>
-      <c r="AA30" s="65"/>
-      <c r="AB30" s="65"/>
-      <c r="AC30" s="65"/>
-      <c r="AD30" s="65"/>
-      <c r="AE30" s="65"/>
-      <c r="AF30" s="65"/>
-      <c r="AG30" s="65"/>
-      <c r="AH30" s="65"/>
-      <c r="AI30" s="65"/>
-      <c r="AJ30" s="65"/>
-      <c r="AK30" s="65"/>
-      <c r="AL30" s="65"/>
-      <c r="AM30" s="65"/>
-      <c r="AN30" s="65"/>
-      <c r="AO30" s="65"/>
-      <c r="AP30" s="65"/>
-      <c r="AQ30" s="65"/>
-      <c r="AR30" s="65"/>
-      <c r="AS30" s="65"/>
-      <c r="AT30" s="65"/>
-      <c r="AU30" s="65"/>
-      <c r="AV30" s="65"/>
-      <c r="AW30" s="65"/>
-      <c r="AX30" s="65"/>
-      <c r="AY30" s="65"/>
-      <c r="AZ30" s="65"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="67"/>
+      <c r="F30" s="67"/>
+      <c r="G30" s="67"/>
+      <c r="H30" s="67"/>
+      <c r="I30" s="67"/>
+      <c r="J30" s="67"/>
+      <c r="K30" s="67"/>
+      <c r="L30" s="67"/>
+      <c r="M30" s="67"/>
+      <c r="N30" s="67"/>
+      <c r="O30" s="67"/>
+      <c r="P30" s="67"/>
+      <c r="Q30" s="67"/>
+      <c r="R30" s="67"/>
+      <c r="S30" s="67"/>
+      <c r="T30" s="67"/>
+      <c r="U30" s="67"/>
+      <c r="V30" s="67"/>
+      <c r="W30" s="67"/>
+      <c r="X30" s="67"/>
+      <c r="Y30" s="67"/>
+      <c r="Z30" s="67"/>
+      <c r="AA30" s="67"/>
+      <c r="AB30" s="67"/>
+      <c r="AC30" s="67"/>
+      <c r="AD30" s="67"/>
+      <c r="AE30" s="67"/>
+      <c r="AF30" s="67"/>
+      <c r="AG30" s="67"/>
+      <c r="AH30" s="67"/>
+      <c r="AI30" s="67"/>
+      <c r="AJ30" s="67"/>
+      <c r="AK30" s="67"/>
+      <c r="AL30" s="67"/>
+      <c r="AM30" s="67"/>
+      <c r="AN30" s="67"/>
+      <c r="AO30" s="67"/>
+      <c r="AP30" s="67"/>
+      <c r="AQ30" s="67"/>
+      <c r="AR30" s="67"/>
+      <c r="AS30" s="67"/>
+      <c r="AT30" s="67"/>
+      <c r="AU30" s="67"/>
+      <c r="AV30" s="67"/>
+      <c r="AW30" s="67"/>
+      <c r="AX30" s="67"/>
+      <c r="AY30" s="67"/>
+      <c r="AZ30" s="67"/>
     </row>
     <row r="31" spans="1:52" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="12"/>
@@ -10644,55 +10644,55 @@
       <c r="C31" s="66" t="s">
         <v>114</v>
       </c>
-      <c r="D31" s="65"/>
-      <c r="E31" s="65"/>
-      <c r="F31" s="65"/>
-      <c r="G31" s="65"/>
-      <c r="H31" s="65"/>
-      <c r="I31" s="65"/>
-      <c r="J31" s="65"/>
-      <c r="K31" s="65"/>
-      <c r="L31" s="65"/>
-      <c r="M31" s="65"/>
-      <c r="N31" s="65"/>
-      <c r="O31" s="65"/>
-      <c r="P31" s="65"/>
-      <c r="Q31" s="65"/>
-      <c r="R31" s="65"/>
-      <c r="S31" s="65"/>
-      <c r="T31" s="65"/>
-      <c r="U31" s="65"/>
-      <c r="V31" s="65"/>
-      <c r="W31" s="65"/>
-      <c r="X31" s="65"/>
-      <c r="Y31" s="65"/>
-      <c r="Z31" s="65"/>
-      <c r="AA31" s="65"/>
-      <c r="AB31" s="65"/>
-      <c r="AC31" s="65"/>
-      <c r="AD31" s="65"/>
-      <c r="AE31" s="65"/>
-      <c r="AF31" s="65"/>
-      <c r="AG31" s="65"/>
-      <c r="AH31" s="65"/>
-      <c r="AI31" s="65"/>
-      <c r="AJ31" s="65"/>
-      <c r="AK31" s="65"/>
-      <c r="AL31" s="65"/>
-      <c r="AM31" s="65"/>
-      <c r="AN31" s="65"/>
-      <c r="AO31" s="65"/>
-      <c r="AP31" s="65"/>
-      <c r="AQ31" s="65"/>
-      <c r="AR31" s="65"/>
-      <c r="AS31" s="65"/>
-      <c r="AT31" s="65"/>
-      <c r="AU31" s="65"/>
-      <c r="AV31" s="65"/>
-      <c r="AW31" s="65"/>
-      <c r="AX31" s="65"/>
-      <c r="AY31" s="65"/>
-      <c r="AZ31" s="65"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="67"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="67"/>
+      <c r="H31" s="67"/>
+      <c r="I31" s="67"/>
+      <c r="J31" s="67"/>
+      <c r="K31" s="67"/>
+      <c r="L31" s="67"/>
+      <c r="M31" s="67"/>
+      <c r="N31" s="67"/>
+      <c r="O31" s="67"/>
+      <c r="P31" s="67"/>
+      <c r="Q31" s="67"/>
+      <c r="R31" s="67"/>
+      <c r="S31" s="67"/>
+      <c r="T31" s="67"/>
+      <c r="U31" s="67"/>
+      <c r="V31" s="67"/>
+      <c r="W31" s="67"/>
+      <c r="X31" s="67"/>
+      <c r="Y31" s="67"/>
+      <c r="Z31" s="67"/>
+      <c r="AA31" s="67"/>
+      <c r="AB31" s="67"/>
+      <c r="AC31" s="67"/>
+      <c r="AD31" s="67"/>
+      <c r="AE31" s="67"/>
+      <c r="AF31" s="67"/>
+      <c r="AG31" s="67"/>
+      <c r="AH31" s="67"/>
+      <c r="AI31" s="67"/>
+      <c r="AJ31" s="67"/>
+      <c r="AK31" s="67"/>
+      <c r="AL31" s="67"/>
+      <c r="AM31" s="67"/>
+      <c r="AN31" s="67"/>
+      <c r="AO31" s="67"/>
+      <c r="AP31" s="67"/>
+      <c r="AQ31" s="67"/>
+      <c r="AR31" s="67"/>
+      <c r="AS31" s="67"/>
+      <c r="AT31" s="67"/>
+      <c r="AU31" s="67"/>
+      <c r="AV31" s="67"/>
+      <c r="AW31" s="67"/>
+      <c r="AX31" s="67"/>
+      <c r="AY31" s="67"/>
+      <c r="AZ31" s="67"/>
     </row>
     <row r="32" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="11"/>
@@ -10714,57 +10714,57 @@
       <c r="A33" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="B33" s="70"/>
-      <c r="C33" s="70"/>
-      <c r="D33" s="70"/>
-      <c r="E33" s="70"/>
-      <c r="F33" s="70"/>
-      <c r="G33" s="70"/>
-      <c r="H33" s="70"/>
-      <c r="I33" s="70"/>
-      <c r="J33" s="70"/>
-      <c r="K33" s="70"/>
-      <c r="L33" s="70"/>
-      <c r="M33" s="70"/>
-      <c r="N33" s="70"/>
-      <c r="O33" s="70"/>
-      <c r="P33" s="70"/>
-      <c r="Q33" s="70"/>
-      <c r="R33" s="70"/>
-      <c r="S33" s="70"/>
-      <c r="T33" s="70"/>
-      <c r="U33" s="70"/>
-      <c r="V33" s="70"/>
-      <c r="W33" s="70"/>
-      <c r="X33" s="70"/>
-      <c r="Y33" s="70"/>
-      <c r="Z33" s="70"/>
-      <c r="AA33" s="70"/>
-      <c r="AB33" s="70"/>
-      <c r="AC33" s="70"/>
-      <c r="AD33" s="70"/>
-      <c r="AE33" s="70"/>
-      <c r="AF33" s="70"/>
-      <c r="AG33" s="70"/>
-      <c r="AH33" s="70"/>
-      <c r="AI33" s="70"/>
-      <c r="AJ33" s="70"/>
-      <c r="AK33" s="70"/>
-      <c r="AL33" s="70"/>
-      <c r="AM33" s="70"/>
-      <c r="AN33" s="70"/>
-      <c r="AO33" s="70"/>
-      <c r="AP33" s="70"/>
-      <c r="AQ33" s="70"/>
-      <c r="AR33" s="70"/>
-      <c r="AS33" s="70"/>
-      <c r="AT33" s="70"/>
-      <c r="AU33" s="70"/>
-      <c r="AV33" s="70"/>
-      <c r="AW33" s="70"/>
-      <c r="AX33" s="70"/>
-      <c r="AY33" s="70"/>
-      <c r="AZ33" s="70"/>
+      <c r="B33" s="72"/>
+      <c r="C33" s="72"/>
+      <c r="D33" s="72"/>
+      <c r="E33" s="72"/>
+      <c r="F33" s="72"/>
+      <c r="G33" s="72"/>
+      <c r="H33" s="72"/>
+      <c r="I33" s="72"/>
+      <c r="J33" s="72"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="72"/>
+      <c r="M33" s="72"/>
+      <c r="N33" s="72"/>
+      <c r="O33" s="72"/>
+      <c r="P33" s="72"/>
+      <c r="Q33" s="72"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="72"/>
+      <c r="T33" s="72"/>
+      <c r="U33" s="72"/>
+      <c r="V33" s="72"/>
+      <c r="W33" s="72"/>
+      <c r="X33" s="72"/>
+      <c r="Y33" s="72"/>
+      <c r="Z33" s="72"/>
+      <c r="AA33" s="72"/>
+      <c r="AB33" s="72"/>
+      <c r="AC33" s="72"/>
+      <c r="AD33" s="72"/>
+      <c r="AE33" s="72"/>
+      <c r="AF33" s="72"/>
+      <c r="AG33" s="72"/>
+      <c r="AH33" s="72"/>
+      <c r="AI33" s="72"/>
+      <c r="AJ33" s="72"/>
+      <c r="AK33" s="72"/>
+      <c r="AL33" s="72"/>
+      <c r="AM33" s="72"/>
+      <c r="AN33" s="72"/>
+      <c r="AO33" s="72"/>
+      <c r="AP33" s="72"/>
+      <c r="AQ33" s="72"/>
+      <c r="AR33" s="72"/>
+      <c r="AS33" s="72"/>
+      <c r="AT33" s="72"/>
+      <c r="AU33" s="72"/>
+      <c r="AV33" s="72"/>
+      <c r="AW33" s="72"/>
+      <c r="AX33" s="72"/>
+      <c r="AY33" s="72"/>
+      <c r="AZ33" s="72"/>
     </row>
     <row r="34" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="28" t="s">
@@ -10774,55 +10774,55 @@
       <c r="C34" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="D34" s="70"/>
-      <c r="E34" s="70"/>
-      <c r="F34" s="70"/>
-      <c r="G34" s="70"/>
-      <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
-      <c r="J34" s="70"/>
-      <c r="K34" s="70"/>
-      <c r="L34" s="70"/>
-      <c r="M34" s="70"/>
-      <c r="N34" s="70"/>
-      <c r="O34" s="70"/>
-      <c r="P34" s="70"/>
-      <c r="Q34" s="70"/>
-      <c r="R34" s="70"/>
-      <c r="S34" s="70"/>
-      <c r="T34" s="70"/>
-      <c r="U34" s="70"/>
-      <c r="V34" s="70"/>
-      <c r="W34" s="70"/>
-      <c r="X34" s="70"/>
-      <c r="Y34" s="70"/>
-      <c r="Z34" s="70"/>
-      <c r="AA34" s="70"/>
-      <c r="AB34" s="70"/>
-      <c r="AC34" s="70"/>
-      <c r="AD34" s="70"/>
-      <c r="AE34" s="70"/>
-      <c r="AF34" s="70"/>
-      <c r="AG34" s="70"/>
-      <c r="AH34" s="70"/>
-      <c r="AI34" s="70"/>
-      <c r="AJ34" s="70"/>
-      <c r="AK34" s="70"/>
-      <c r="AL34" s="70"/>
-      <c r="AM34" s="70"/>
-      <c r="AN34" s="70"/>
-      <c r="AO34" s="70"/>
-      <c r="AP34" s="70"/>
-      <c r="AQ34" s="70"/>
-      <c r="AR34" s="70"/>
-      <c r="AS34" s="70"/>
-      <c r="AT34" s="70"/>
-      <c r="AU34" s="70"/>
-      <c r="AV34" s="70"/>
-      <c r="AW34" s="70"/>
-      <c r="AX34" s="70"/>
-      <c r="AY34" s="70"/>
-      <c r="AZ34" s="70"/>
+      <c r="D34" s="72"/>
+      <c r="E34" s="72"/>
+      <c r="F34" s="72"/>
+      <c r="G34" s="72"/>
+      <c r="H34" s="72"/>
+      <c r="I34" s="72"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="72"/>
+      <c r="L34" s="72"/>
+      <c r="M34" s="72"/>
+      <c r="N34" s="72"/>
+      <c r="O34" s="72"/>
+      <c r="P34" s="72"/>
+      <c r="Q34" s="72"/>
+      <c r="R34" s="72"/>
+      <c r="S34" s="72"/>
+      <c r="T34" s="72"/>
+      <c r="U34" s="72"/>
+      <c r="V34" s="72"/>
+      <c r="W34" s="72"/>
+      <c r="X34" s="72"/>
+      <c r="Y34" s="72"/>
+      <c r="Z34" s="72"/>
+      <c r="AA34" s="72"/>
+      <c r="AB34" s="72"/>
+      <c r="AC34" s="72"/>
+      <c r="AD34" s="72"/>
+      <c r="AE34" s="72"/>
+      <c r="AF34" s="72"/>
+      <c r="AG34" s="72"/>
+      <c r="AH34" s="72"/>
+      <c r="AI34" s="72"/>
+      <c r="AJ34" s="72"/>
+      <c r="AK34" s="72"/>
+      <c r="AL34" s="72"/>
+      <c r="AM34" s="72"/>
+      <c r="AN34" s="72"/>
+      <c r="AO34" s="72"/>
+      <c r="AP34" s="72"/>
+      <c r="AQ34" s="72"/>
+      <c r="AR34" s="72"/>
+      <c r="AS34" s="72"/>
+      <c r="AT34" s="72"/>
+      <c r="AU34" s="72"/>
+      <c r="AV34" s="72"/>
+      <c r="AW34" s="72"/>
+      <c r="AX34" s="72"/>
+      <c r="AY34" s="72"/>
+      <c r="AZ34" s="72"/>
     </row>
     <row r="35" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="12"/>
@@ -10830,55 +10830,55 @@
       <c r="C35" s="66" t="s">
         <v>115</v>
       </c>
-      <c r="D35" s="65"/>
-      <c r="E35" s="65"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="65"/>
-      <c r="H35" s="65"/>
-      <c r="I35" s="65"/>
-      <c r="J35" s="65"/>
-      <c r="K35" s="65"/>
-      <c r="L35" s="65"/>
-      <c r="M35" s="65"/>
-      <c r="N35" s="65"/>
-      <c r="O35" s="65"/>
-      <c r="P35" s="65"/>
-      <c r="Q35" s="65"/>
-      <c r="R35" s="65"/>
-      <c r="S35" s="65"/>
-      <c r="T35" s="65"/>
-      <c r="U35" s="65"/>
-      <c r="V35" s="65"/>
-      <c r="W35" s="65"/>
-      <c r="X35" s="65"/>
-      <c r="Y35" s="65"/>
-      <c r="Z35" s="65"/>
-      <c r="AA35" s="65"/>
-      <c r="AB35" s="65"/>
-      <c r="AC35" s="65"/>
-      <c r="AD35" s="65"/>
-      <c r="AE35" s="65"/>
-      <c r="AF35" s="65"/>
-      <c r="AG35" s="65"/>
-      <c r="AH35" s="65"/>
-      <c r="AI35" s="65"/>
-      <c r="AJ35" s="65"/>
-      <c r="AK35" s="65"/>
-      <c r="AL35" s="65"/>
-      <c r="AM35" s="65"/>
-      <c r="AN35" s="65"/>
-      <c r="AO35" s="65"/>
-      <c r="AP35" s="65"/>
-      <c r="AQ35" s="65"/>
-      <c r="AR35" s="65"/>
-      <c r="AS35" s="65"/>
-      <c r="AT35" s="65"/>
-      <c r="AU35" s="65"/>
-      <c r="AV35" s="65"/>
-      <c r="AW35" s="65"/>
-      <c r="AX35" s="65"/>
-      <c r="AY35" s="65"/>
-      <c r="AZ35" s="65"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="67"/>
+      <c r="F35" s="67"/>
+      <c r="G35" s="67"/>
+      <c r="H35" s="67"/>
+      <c r="I35" s="67"/>
+      <c r="J35" s="67"/>
+      <c r="K35" s="67"/>
+      <c r="L35" s="67"/>
+      <c r="M35" s="67"/>
+      <c r="N35" s="67"/>
+      <c r="O35" s="67"/>
+      <c r="P35" s="67"/>
+      <c r="Q35" s="67"/>
+      <c r="R35" s="67"/>
+      <c r="S35" s="67"/>
+      <c r="T35" s="67"/>
+      <c r="U35" s="67"/>
+      <c r="V35" s="67"/>
+      <c r="W35" s="67"/>
+      <c r="X35" s="67"/>
+      <c r="Y35" s="67"/>
+      <c r="Z35" s="67"/>
+      <c r="AA35" s="67"/>
+      <c r="AB35" s="67"/>
+      <c r="AC35" s="67"/>
+      <c r="AD35" s="67"/>
+      <c r="AE35" s="67"/>
+      <c r="AF35" s="67"/>
+      <c r="AG35" s="67"/>
+      <c r="AH35" s="67"/>
+      <c r="AI35" s="67"/>
+      <c r="AJ35" s="67"/>
+      <c r="AK35" s="67"/>
+      <c r="AL35" s="67"/>
+      <c r="AM35" s="67"/>
+      <c r="AN35" s="67"/>
+      <c r="AO35" s="67"/>
+      <c r="AP35" s="67"/>
+      <c r="AQ35" s="67"/>
+      <c r="AR35" s="67"/>
+      <c r="AS35" s="67"/>
+      <c r="AT35" s="67"/>
+      <c r="AU35" s="67"/>
+      <c r="AV35" s="67"/>
+      <c r="AW35" s="67"/>
+      <c r="AX35" s="67"/>
+      <c r="AY35" s="67"/>
+      <c r="AZ35" s="67"/>
     </row>
     <row r="36" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="12"/>
@@ -10886,55 +10886,55 @@
       <c r="C36" s="66" t="s">
         <v>116</v>
       </c>
-      <c r="D36" s="65"/>
-      <c r="E36" s="65"/>
-      <c r="F36" s="65"/>
-      <c r="G36" s="65"/>
-      <c r="H36" s="65"/>
-      <c r="I36" s="65"/>
-      <c r="J36" s="65"/>
-      <c r="K36" s="65"/>
-      <c r="L36" s="65"/>
-      <c r="M36" s="65"/>
-      <c r="N36" s="65"/>
-      <c r="O36" s="65"/>
-      <c r="P36" s="65"/>
-      <c r="Q36" s="65"/>
-      <c r="R36" s="65"/>
-      <c r="S36" s="65"/>
-      <c r="T36" s="65"/>
-      <c r="U36" s="65"/>
-      <c r="V36" s="65"/>
-      <c r="W36" s="65"/>
-      <c r="X36" s="65"/>
-      <c r="Y36" s="65"/>
-      <c r="Z36" s="65"/>
-      <c r="AA36" s="65"/>
-      <c r="AB36" s="65"/>
-      <c r="AC36" s="65"/>
-      <c r="AD36" s="65"/>
-      <c r="AE36" s="65"/>
-      <c r="AF36" s="65"/>
-      <c r="AG36" s="65"/>
-      <c r="AH36" s="65"/>
-      <c r="AI36" s="65"/>
-      <c r="AJ36" s="65"/>
-      <c r="AK36" s="65"/>
-      <c r="AL36" s="65"/>
-      <c r="AM36" s="65"/>
-      <c r="AN36" s="65"/>
-      <c r="AO36" s="65"/>
-      <c r="AP36" s="65"/>
-      <c r="AQ36" s="65"/>
-      <c r="AR36" s="65"/>
-      <c r="AS36" s="65"/>
-      <c r="AT36" s="65"/>
-      <c r="AU36" s="65"/>
-      <c r="AV36" s="65"/>
-      <c r="AW36" s="65"/>
-      <c r="AX36" s="65"/>
-      <c r="AY36" s="65"/>
-      <c r="AZ36" s="65"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="67"/>
+      <c r="H36" s="67"/>
+      <c r="I36" s="67"/>
+      <c r="J36" s="67"/>
+      <c r="K36" s="67"/>
+      <c r="L36" s="67"/>
+      <c r="M36" s="67"/>
+      <c r="N36" s="67"/>
+      <c r="O36" s="67"/>
+      <c r="P36" s="67"/>
+      <c r="Q36" s="67"/>
+      <c r="R36" s="67"/>
+      <c r="S36" s="67"/>
+      <c r="T36" s="67"/>
+      <c r="U36" s="67"/>
+      <c r="V36" s="67"/>
+      <c r="W36" s="67"/>
+      <c r="X36" s="67"/>
+      <c r="Y36" s="67"/>
+      <c r="Z36" s="67"/>
+      <c r="AA36" s="67"/>
+      <c r="AB36" s="67"/>
+      <c r="AC36" s="67"/>
+      <c r="AD36" s="67"/>
+      <c r="AE36" s="67"/>
+      <c r="AF36" s="67"/>
+      <c r="AG36" s="67"/>
+      <c r="AH36" s="67"/>
+      <c r="AI36" s="67"/>
+      <c r="AJ36" s="67"/>
+      <c r="AK36" s="67"/>
+      <c r="AL36" s="67"/>
+      <c r="AM36" s="67"/>
+      <c r="AN36" s="67"/>
+      <c r="AO36" s="67"/>
+      <c r="AP36" s="67"/>
+      <c r="AQ36" s="67"/>
+      <c r="AR36" s="67"/>
+      <c r="AS36" s="67"/>
+      <c r="AT36" s="67"/>
+      <c r="AU36" s="67"/>
+      <c r="AV36" s="67"/>
+      <c r="AW36" s="67"/>
+      <c r="AX36" s="67"/>
+      <c r="AY36" s="67"/>
+      <c r="AZ36" s="67"/>
     </row>
     <row r="37" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="12"/>
@@ -10942,167 +10942,167 @@
       <c r="C37" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="D37" s="65"/>
-      <c r="E37" s="65"/>
-      <c r="F37" s="65"/>
-      <c r="G37" s="65"/>
-      <c r="H37" s="65"/>
-      <c r="I37" s="65"/>
-      <c r="J37" s="65"/>
-      <c r="K37" s="65"/>
-      <c r="L37" s="65"/>
-      <c r="M37" s="65"/>
-      <c r="N37" s="65"/>
-      <c r="O37" s="65"/>
-      <c r="P37" s="65"/>
-      <c r="Q37" s="65"/>
-      <c r="R37" s="65"/>
-      <c r="S37" s="65"/>
-      <c r="T37" s="65"/>
-      <c r="U37" s="65"/>
-      <c r="V37" s="65"/>
-      <c r="W37" s="65"/>
-      <c r="X37" s="65"/>
-      <c r="Y37" s="65"/>
-      <c r="Z37" s="65"/>
-      <c r="AA37" s="65"/>
-      <c r="AB37" s="65"/>
-      <c r="AC37" s="65"/>
-      <c r="AD37" s="65"/>
-      <c r="AE37" s="65"/>
-      <c r="AF37" s="65"/>
-      <c r="AG37" s="65"/>
-      <c r="AH37" s="65"/>
-      <c r="AI37" s="65"/>
-      <c r="AJ37" s="65"/>
-      <c r="AK37" s="65"/>
-      <c r="AL37" s="65"/>
-      <c r="AM37" s="65"/>
-      <c r="AN37" s="65"/>
-      <c r="AO37" s="65"/>
-      <c r="AP37" s="65"/>
-      <c r="AQ37" s="65"/>
-      <c r="AR37" s="65"/>
-      <c r="AS37" s="65"/>
-      <c r="AT37" s="65"/>
-      <c r="AU37" s="65"/>
-      <c r="AV37" s="65"/>
-      <c r="AW37" s="65"/>
-      <c r="AX37" s="65"/>
-      <c r="AY37" s="65"/>
-      <c r="AZ37" s="65"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="67"/>
+      <c r="F37" s="67"/>
+      <c r="G37" s="67"/>
+      <c r="H37" s="67"/>
+      <c r="I37" s="67"/>
+      <c r="J37" s="67"/>
+      <c r="K37" s="67"/>
+      <c r="L37" s="67"/>
+      <c r="M37" s="67"/>
+      <c r="N37" s="67"/>
+      <c r="O37" s="67"/>
+      <c r="P37" s="67"/>
+      <c r="Q37" s="67"/>
+      <c r="R37" s="67"/>
+      <c r="S37" s="67"/>
+      <c r="T37" s="67"/>
+      <c r="U37" s="67"/>
+      <c r="V37" s="67"/>
+      <c r="W37" s="67"/>
+      <c r="X37" s="67"/>
+      <c r="Y37" s="67"/>
+      <c r="Z37" s="67"/>
+      <c r="AA37" s="67"/>
+      <c r="AB37" s="67"/>
+      <c r="AC37" s="67"/>
+      <c r="AD37" s="67"/>
+      <c r="AE37" s="67"/>
+      <c r="AF37" s="67"/>
+      <c r="AG37" s="67"/>
+      <c r="AH37" s="67"/>
+      <c r="AI37" s="67"/>
+      <c r="AJ37" s="67"/>
+      <c r="AK37" s="67"/>
+      <c r="AL37" s="67"/>
+      <c r="AM37" s="67"/>
+      <c r="AN37" s="67"/>
+      <c r="AO37" s="67"/>
+      <c r="AP37" s="67"/>
+      <c r="AQ37" s="67"/>
+      <c r="AR37" s="67"/>
+      <c r="AS37" s="67"/>
+      <c r="AT37" s="67"/>
+      <c r="AU37" s="67"/>
+      <c r="AV37" s="67"/>
+      <c r="AW37" s="67"/>
+      <c r="AX37" s="67"/>
+      <c r="AY37" s="67"/>
+      <c r="AZ37" s="67"/>
     </row>
     <row r="38" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="12"/>
       <c r="B38" s="11"/>
-      <c r="C38" s="68" t="s">
+      <c r="C38" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="69"/>
-      <c r="E38" s="69"/>
-      <c r="F38" s="69"/>
-      <c r="G38" s="69"/>
-      <c r="H38" s="69"/>
-      <c r="I38" s="69"/>
-      <c r="J38" s="69"/>
-      <c r="K38" s="69"/>
-      <c r="L38" s="69"/>
-      <c r="M38" s="69"/>
-      <c r="N38" s="69"/>
-      <c r="O38" s="69"/>
-      <c r="P38" s="69"/>
-      <c r="Q38" s="69"/>
-      <c r="R38" s="69"/>
-      <c r="S38" s="69"/>
-      <c r="T38" s="69"/>
-      <c r="U38" s="69"/>
-      <c r="V38" s="69"/>
-      <c r="W38" s="69"/>
-      <c r="X38" s="69"/>
-      <c r="Y38" s="69"/>
-      <c r="Z38" s="69"/>
-      <c r="AA38" s="69"/>
-      <c r="AB38" s="69"/>
-      <c r="AC38" s="69"/>
-      <c r="AD38" s="69"/>
-      <c r="AE38" s="69"/>
-      <c r="AF38" s="69"/>
-      <c r="AG38" s="69"/>
-      <c r="AH38" s="69"/>
-      <c r="AI38" s="69"/>
-      <c r="AJ38" s="69"/>
-      <c r="AK38" s="69"/>
-      <c r="AL38" s="69"/>
-      <c r="AM38" s="69"/>
-      <c r="AN38" s="69"/>
-      <c r="AO38" s="69"/>
-      <c r="AP38" s="69"/>
-      <c r="AQ38" s="69"/>
-      <c r="AR38" s="69"/>
-      <c r="AS38" s="69"/>
-      <c r="AT38" s="69"/>
-      <c r="AU38" s="69"/>
-      <c r="AV38" s="69"/>
-      <c r="AW38" s="69"/>
-      <c r="AX38" s="69"/>
-      <c r="AY38" s="69"/>
-      <c r="AZ38" s="69"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="71"/>
+      <c r="L38" s="71"/>
+      <c r="M38" s="71"/>
+      <c r="N38" s="71"/>
+      <c r="O38" s="71"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="71"/>
+      <c r="S38" s="71"/>
+      <c r="T38" s="71"/>
+      <c r="U38" s="71"/>
+      <c r="V38" s="71"/>
+      <c r="W38" s="71"/>
+      <c r="X38" s="71"/>
+      <c r="Y38" s="71"/>
+      <c r="Z38" s="71"/>
+      <c r="AA38" s="71"/>
+      <c r="AB38" s="71"/>
+      <c r="AC38" s="71"/>
+      <c r="AD38" s="71"/>
+      <c r="AE38" s="71"/>
+      <c r="AF38" s="71"/>
+      <c r="AG38" s="71"/>
+      <c r="AH38" s="71"/>
+      <c r="AI38" s="71"/>
+      <c r="AJ38" s="71"/>
+      <c r="AK38" s="71"/>
+      <c r="AL38" s="71"/>
+      <c r="AM38" s="71"/>
+      <c r="AN38" s="71"/>
+      <c r="AO38" s="71"/>
+      <c r="AP38" s="71"/>
+      <c r="AQ38" s="71"/>
+      <c r="AR38" s="71"/>
+      <c r="AS38" s="71"/>
+      <c r="AT38" s="71"/>
+      <c r="AU38" s="71"/>
+      <c r="AV38" s="71"/>
+      <c r="AW38" s="71"/>
+      <c r="AX38" s="71"/>
+      <c r="AY38" s="71"/>
+      <c r="AZ38" s="71"/>
     </row>
     <row r="39" spans="1:52" ht="18.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="12"/>
       <c r="B39" s="11"/>
-      <c r="C39" s="65" t="s">
+      <c r="C39" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="D39" s="65"/>
-      <c r="E39" s="65"/>
-      <c r="F39" s="65"/>
-      <c r="G39" s="65"/>
-      <c r="H39" s="65"/>
-      <c r="I39" s="65"/>
-      <c r="J39" s="65"/>
-      <c r="K39" s="65"/>
-      <c r="L39" s="65"/>
-      <c r="M39" s="65"/>
-      <c r="N39" s="65"/>
-      <c r="O39" s="65"/>
-      <c r="P39" s="65"/>
-      <c r="Q39" s="65"/>
-      <c r="R39" s="65"/>
-      <c r="S39" s="65"/>
-      <c r="T39" s="65"/>
-      <c r="U39" s="65"/>
-      <c r="V39" s="65"/>
-      <c r="W39" s="65"/>
-      <c r="X39" s="65"/>
-      <c r="Y39" s="65"/>
-      <c r="Z39" s="65"/>
-      <c r="AA39" s="65"/>
-      <c r="AB39" s="65"/>
-      <c r="AC39" s="65"/>
-      <c r="AD39" s="65"/>
-      <c r="AE39" s="65"/>
-      <c r="AF39" s="65"/>
-      <c r="AG39" s="65"/>
-      <c r="AH39" s="65"/>
-      <c r="AI39" s="65"/>
-      <c r="AJ39" s="65"/>
-      <c r="AK39" s="65"/>
-      <c r="AL39" s="65"/>
-      <c r="AM39" s="65"/>
-      <c r="AN39" s="65"/>
-      <c r="AO39" s="65"/>
-      <c r="AP39" s="65"/>
-      <c r="AQ39" s="65"/>
-      <c r="AR39" s="65"/>
-      <c r="AS39" s="65"/>
-      <c r="AT39" s="65"/>
-      <c r="AU39" s="65"/>
-      <c r="AV39" s="65"/>
-      <c r="AW39" s="65"/>
-      <c r="AX39" s="65"/>
-      <c r="AY39" s="65"/>
-      <c r="AZ39" s="65"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="67"/>
+      <c r="F39" s="67"/>
+      <c r="G39" s="67"/>
+      <c r="H39" s="67"/>
+      <c r="I39" s="67"/>
+      <c r="J39" s="67"/>
+      <c r="K39" s="67"/>
+      <c r="L39" s="67"/>
+      <c r="M39" s="67"/>
+      <c r="N39" s="67"/>
+      <c r="O39" s="67"/>
+      <c r="P39" s="67"/>
+      <c r="Q39" s="67"/>
+      <c r="R39" s="67"/>
+      <c r="S39" s="67"/>
+      <c r="T39" s="67"/>
+      <c r="U39" s="67"/>
+      <c r="V39" s="67"/>
+      <c r="W39" s="67"/>
+      <c r="X39" s="67"/>
+      <c r="Y39" s="67"/>
+      <c r="Z39" s="67"/>
+      <c r="AA39" s="67"/>
+      <c r="AB39" s="67"/>
+      <c r="AC39" s="67"/>
+      <c r="AD39" s="67"/>
+      <c r="AE39" s="67"/>
+      <c r="AF39" s="67"/>
+      <c r="AG39" s="67"/>
+      <c r="AH39" s="67"/>
+      <c r="AI39" s="67"/>
+      <c r="AJ39" s="67"/>
+      <c r="AK39" s="67"/>
+      <c r="AL39" s="67"/>
+      <c r="AM39" s="67"/>
+      <c r="AN39" s="67"/>
+      <c r="AO39" s="67"/>
+      <c r="AP39" s="67"/>
+      <c r="AQ39" s="67"/>
+      <c r="AR39" s="67"/>
+      <c r="AS39" s="67"/>
+      <c r="AT39" s="67"/>
+      <c r="AU39" s="67"/>
+      <c r="AV39" s="67"/>
+      <c r="AW39" s="67"/>
+      <c r="AX39" s="67"/>
+      <c r="AY39" s="67"/>
+      <c r="AZ39" s="67"/>
     </row>
     <row r="40" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="12"/>
@@ -11140,1289 +11140,1289 @@
       <c r="A42" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="B42" s="70"/>
-      <c r="C42" s="70"/>
-      <c r="D42" s="70"/>
-      <c r="E42" s="70"/>
-      <c r="F42" s="70"/>
-      <c r="G42" s="70"/>
-      <c r="H42" s="70"/>
-      <c r="I42" s="70"/>
-      <c r="J42" s="70"/>
-      <c r="K42" s="70"/>
-      <c r="L42" s="70"/>
-      <c r="M42" s="70"/>
-      <c r="N42" s="70"/>
-      <c r="O42" s="70"/>
-      <c r="P42" s="70"/>
-      <c r="Q42" s="70"/>
-      <c r="R42" s="70"/>
-      <c r="S42" s="70"/>
-      <c r="T42" s="70"/>
-      <c r="U42" s="70"/>
-      <c r="V42" s="70"/>
-      <c r="W42" s="70"/>
-      <c r="X42" s="70"/>
-      <c r="Y42" s="70"/>
-      <c r="Z42" s="70"/>
-      <c r="AA42" s="70"/>
-      <c r="AB42" s="70"/>
-      <c r="AC42" s="70"/>
-      <c r="AD42" s="70"/>
-      <c r="AE42" s="70"/>
-      <c r="AF42" s="70"/>
-      <c r="AG42" s="70"/>
-      <c r="AH42" s="70"/>
-      <c r="AI42" s="70"/>
-      <c r="AJ42" s="70"/>
-      <c r="AK42" s="70"/>
-      <c r="AL42" s="70"/>
-      <c r="AM42" s="70"/>
-      <c r="AN42" s="70"/>
-      <c r="AO42" s="70"/>
-      <c r="AP42" s="70"/>
-      <c r="AQ42" s="70"/>
-      <c r="AR42" s="70"/>
-      <c r="AS42" s="70"/>
-      <c r="AT42" s="70"/>
-      <c r="AU42" s="70"/>
-      <c r="AV42" s="70"/>
-      <c r="AW42" s="70"/>
-      <c r="AX42" s="70"/>
-      <c r="AY42" s="70"/>
-      <c r="AZ42" s="70"/>
+      <c r="B42" s="72"/>
+      <c r="C42" s="72"/>
+      <c r="D42" s="72"/>
+      <c r="E42" s="72"/>
+      <c r="F42" s="72"/>
+      <c r="G42" s="72"/>
+      <c r="H42" s="72"/>
+      <c r="I42" s="72"/>
+      <c r="J42" s="72"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="72"/>
+      <c r="M42" s="72"/>
+      <c r="N42" s="72"/>
+      <c r="O42" s="72"/>
+      <c r="P42" s="72"/>
+      <c r="Q42" s="72"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="72"/>
+      <c r="T42" s="72"/>
+      <c r="U42" s="72"/>
+      <c r="V42" s="72"/>
+      <c r="W42" s="72"/>
+      <c r="X42" s="72"/>
+      <c r="Y42" s="72"/>
+      <c r="Z42" s="72"/>
+      <c r="AA42" s="72"/>
+      <c r="AB42" s="72"/>
+      <c r="AC42" s="72"/>
+      <c r="AD42" s="72"/>
+      <c r="AE42" s="72"/>
+      <c r="AF42" s="72"/>
+      <c r="AG42" s="72"/>
+      <c r="AH42" s="72"/>
+      <c r="AI42" s="72"/>
+      <c r="AJ42" s="72"/>
+      <c r="AK42" s="72"/>
+      <c r="AL42" s="72"/>
+      <c r="AM42" s="72"/>
+      <c r="AN42" s="72"/>
+      <c r="AO42" s="72"/>
+      <c r="AP42" s="72"/>
+      <c r="AQ42" s="72"/>
+      <c r="AR42" s="72"/>
+      <c r="AS42" s="72"/>
+      <c r="AT42" s="72"/>
+      <c r="AU42" s="72"/>
+      <c r="AV42" s="72"/>
+      <c r="AW42" s="72"/>
+      <c r="AX42" s="72"/>
+      <c r="AY42" s="72"/>
+      <c r="AZ42" s="72"/>
     </row>
     <row r="43" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="14"/>
       <c r="B43" s="11"/>
-      <c r="C43" s="64" t="s">
+      <c r="C43" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="D43" s="65"/>
-      <c r="E43" s="65"/>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="65"/>
-      <c r="K43" s="65"/>
-      <c r="L43" s="65"/>
-      <c r="M43" s="65"/>
-      <c r="N43" s="65"/>
-      <c r="O43" s="65"/>
-      <c r="P43" s="65"/>
-      <c r="Q43" s="65"/>
-      <c r="R43" s="65"/>
-      <c r="S43" s="65"/>
-      <c r="T43" s="65"/>
-      <c r="U43" s="65"/>
-      <c r="V43" s="65"/>
-      <c r="W43" s="65"/>
-      <c r="X43" s="65"/>
-      <c r="Y43" s="65"/>
-      <c r="Z43" s="65"/>
-      <c r="AA43" s="65"/>
-      <c r="AB43" s="65"/>
-      <c r="AC43" s="65"/>
-      <c r="AD43" s="65"/>
-      <c r="AE43" s="65"/>
-      <c r="AF43" s="65"/>
-      <c r="AG43" s="65"/>
-      <c r="AH43" s="65"/>
-      <c r="AI43" s="65"/>
-      <c r="AJ43" s="65"/>
-      <c r="AK43" s="65"/>
-      <c r="AL43" s="65"/>
-      <c r="AM43" s="65"/>
-      <c r="AN43" s="65"/>
-      <c r="AO43" s="65"/>
-      <c r="AP43" s="65"/>
-      <c r="AQ43" s="65"/>
-      <c r="AR43" s="65"/>
-      <c r="AS43" s="65"/>
-      <c r="AT43" s="65"/>
-      <c r="AU43" s="65"/>
-      <c r="AV43" s="65"/>
-      <c r="AW43" s="65"/>
-      <c r="AX43" s="65"/>
-      <c r="AY43" s="65"/>
-      <c r="AZ43" s="65"/>
+      <c r="D43" s="67"/>
+      <c r="E43" s="67"/>
+      <c r="F43" s="67"/>
+      <c r="G43" s="67"/>
+      <c r="H43" s="67"/>
+      <c r="I43" s="67"/>
+      <c r="J43" s="67"/>
+      <c r="K43" s="67"/>
+      <c r="L43" s="67"/>
+      <c r="M43" s="67"/>
+      <c r="N43" s="67"/>
+      <c r="O43" s="67"/>
+      <c r="P43" s="67"/>
+      <c r="Q43" s="67"/>
+      <c r="R43" s="67"/>
+      <c r="S43" s="67"/>
+      <c r="T43" s="67"/>
+      <c r="U43" s="67"/>
+      <c r="V43" s="67"/>
+      <c r="W43" s="67"/>
+      <c r="X43" s="67"/>
+      <c r="Y43" s="67"/>
+      <c r="Z43" s="67"/>
+      <c r="AA43" s="67"/>
+      <c r="AB43" s="67"/>
+      <c r="AC43" s="67"/>
+      <c r="AD43" s="67"/>
+      <c r="AE43" s="67"/>
+      <c r="AF43" s="67"/>
+      <c r="AG43" s="67"/>
+      <c r="AH43" s="67"/>
+      <c r="AI43" s="67"/>
+      <c r="AJ43" s="67"/>
+      <c r="AK43" s="67"/>
+      <c r="AL43" s="67"/>
+      <c r="AM43" s="67"/>
+      <c r="AN43" s="67"/>
+      <c r="AO43" s="67"/>
+      <c r="AP43" s="67"/>
+      <c r="AQ43" s="67"/>
+      <c r="AR43" s="67"/>
+      <c r="AS43" s="67"/>
+      <c r="AT43" s="67"/>
+      <c r="AU43" s="67"/>
+      <c r="AV43" s="67"/>
+      <c r="AW43" s="67"/>
+      <c r="AX43" s="67"/>
+      <c r="AY43" s="67"/>
+      <c r="AZ43" s="67"/>
     </row>
     <row r="44" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="11"/>
       <c r="B44" s="11"/>
-      <c r="C44" s="64" t="s">
+      <c r="C44" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="D44" s="65"/>
-      <c r="E44" s="65"/>
-      <c r="F44" s="65"/>
-      <c r="G44" s="65"/>
-      <c r="H44" s="65"/>
-      <c r="I44" s="65"/>
-      <c r="J44" s="65"/>
-      <c r="K44" s="65"/>
-      <c r="L44" s="65"/>
-      <c r="M44" s="65"/>
-      <c r="N44" s="65"/>
-      <c r="O44" s="65"/>
-      <c r="P44" s="65"/>
-      <c r="Q44" s="65"/>
-      <c r="R44" s="65"/>
-      <c r="S44" s="65"/>
-      <c r="T44" s="65"/>
-      <c r="U44" s="65"/>
-      <c r="V44" s="65"/>
-      <c r="W44" s="65"/>
-      <c r="X44" s="65"/>
-      <c r="Y44" s="65"/>
-      <c r="Z44" s="65"/>
-      <c r="AA44" s="65"/>
-      <c r="AB44" s="65"/>
-      <c r="AC44" s="65"/>
-      <c r="AD44" s="65"/>
-      <c r="AE44" s="65"/>
-      <c r="AF44" s="65"/>
-      <c r="AG44" s="65"/>
-      <c r="AH44" s="65"/>
-      <c r="AI44" s="65"/>
-      <c r="AJ44" s="65"/>
-      <c r="AK44" s="65"/>
-      <c r="AL44" s="65"/>
-      <c r="AM44" s="65"/>
-      <c r="AN44" s="65"/>
-      <c r="AO44" s="65"/>
-      <c r="AP44" s="65"/>
-      <c r="AQ44" s="65"/>
-      <c r="AR44" s="65"/>
-      <c r="AS44" s="65"/>
-      <c r="AT44" s="65"/>
-      <c r="AU44" s="65"/>
-      <c r="AV44" s="65"/>
-      <c r="AW44" s="65"/>
-      <c r="AX44" s="65"/>
-      <c r="AY44" s="65"/>
-      <c r="AZ44" s="65"/>
+      <c r="D44" s="67"/>
+      <c r="E44" s="67"/>
+      <c r="F44" s="67"/>
+      <c r="G44" s="67"/>
+      <c r="H44" s="67"/>
+      <c r="I44" s="67"/>
+      <c r="J44" s="67"/>
+      <c r="K44" s="67"/>
+      <c r="L44" s="67"/>
+      <c r="M44" s="67"/>
+      <c r="N44" s="67"/>
+      <c r="O44" s="67"/>
+      <c r="P44" s="67"/>
+      <c r="Q44" s="67"/>
+      <c r="R44" s="67"/>
+      <c r="S44" s="67"/>
+      <c r="T44" s="67"/>
+      <c r="U44" s="67"/>
+      <c r="V44" s="67"/>
+      <c r="W44" s="67"/>
+      <c r="X44" s="67"/>
+      <c r="Y44" s="67"/>
+      <c r="Z44" s="67"/>
+      <c r="AA44" s="67"/>
+      <c r="AB44" s="67"/>
+      <c r="AC44" s="67"/>
+      <c r="AD44" s="67"/>
+      <c r="AE44" s="67"/>
+      <c r="AF44" s="67"/>
+      <c r="AG44" s="67"/>
+      <c r="AH44" s="67"/>
+      <c r="AI44" s="67"/>
+      <c r="AJ44" s="67"/>
+      <c r="AK44" s="67"/>
+      <c r="AL44" s="67"/>
+      <c r="AM44" s="67"/>
+      <c r="AN44" s="67"/>
+      <c r="AO44" s="67"/>
+      <c r="AP44" s="67"/>
+      <c r="AQ44" s="67"/>
+      <c r="AR44" s="67"/>
+      <c r="AS44" s="67"/>
+      <c r="AT44" s="67"/>
+      <c r="AU44" s="67"/>
+      <c r="AV44" s="67"/>
+      <c r="AW44" s="67"/>
+      <c r="AX44" s="67"/>
+      <c r="AY44" s="67"/>
+      <c r="AZ44" s="67"/>
     </row>
     <row r="45" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="11"/>
       <c r="B45" s="11"/>
-      <c r="C45" s="64" t="s">
+      <c r="C45" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="D45" s="65"/>
-      <c r="E45" s="65"/>
-      <c r="F45" s="65"/>
-      <c r="G45" s="65"/>
-      <c r="H45" s="65"/>
-      <c r="I45" s="65"/>
-      <c r="J45" s="65"/>
-      <c r="K45" s="65"/>
-      <c r="L45" s="65"/>
-      <c r="M45" s="65"/>
-      <c r="N45" s="65"/>
-      <c r="O45" s="65"/>
-      <c r="P45" s="65"/>
-      <c r="Q45" s="65"/>
-      <c r="R45" s="65"/>
-      <c r="S45" s="65"/>
-      <c r="T45" s="65"/>
-      <c r="U45" s="65"/>
-      <c r="V45" s="65"/>
-      <c r="W45" s="65"/>
-      <c r="X45" s="65"/>
-      <c r="Y45" s="65"/>
-      <c r="Z45" s="65"/>
-      <c r="AA45" s="65"/>
-      <c r="AB45" s="65"/>
-      <c r="AC45" s="65"/>
-      <c r="AD45" s="65"/>
-      <c r="AE45" s="65"/>
-      <c r="AF45" s="65"/>
-      <c r="AG45" s="65"/>
-      <c r="AH45" s="65"/>
-      <c r="AI45" s="65"/>
-      <c r="AJ45" s="65"/>
-      <c r="AK45" s="65"/>
-      <c r="AL45" s="65"/>
-      <c r="AM45" s="65"/>
-      <c r="AN45" s="65"/>
-      <c r="AO45" s="65"/>
-      <c r="AP45" s="65"/>
-      <c r="AQ45" s="65"/>
-      <c r="AR45" s="65"/>
-      <c r="AS45" s="65"/>
-      <c r="AT45" s="65"/>
-      <c r="AU45" s="65"/>
-      <c r="AV45" s="65"/>
-      <c r="AW45" s="65"/>
-      <c r="AX45" s="65"/>
-      <c r="AY45" s="65"/>
-      <c r="AZ45" s="65"/>
+      <c r="D45" s="67"/>
+      <c r="E45" s="67"/>
+      <c r="F45" s="67"/>
+      <c r="G45" s="67"/>
+      <c r="H45" s="67"/>
+      <c r="I45" s="67"/>
+      <c r="J45" s="67"/>
+      <c r="K45" s="67"/>
+      <c r="L45" s="67"/>
+      <c r="M45" s="67"/>
+      <c r="N45" s="67"/>
+      <c r="O45" s="67"/>
+      <c r="P45" s="67"/>
+      <c r="Q45" s="67"/>
+      <c r="R45" s="67"/>
+      <c r="S45" s="67"/>
+      <c r="T45" s="67"/>
+      <c r="U45" s="67"/>
+      <c r="V45" s="67"/>
+      <c r="W45" s="67"/>
+      <c r="X45" s="67"/>
+      <c r="Y45" s="67"/>
+      <c r="Z45" s="67"/>
+      <c r="AA45" s="67"/>
+      <c r="AB45" s="67"/>
+      <c r="AC45" s="67"/>
+      <c r="AD45" s="67"/>
+      <c r="AE45" s="67"/>
+      <c r="AF45" s="67"/>
+      <c r="AG45" s="67"/>
+      <c r="AH45" s="67"/>
+      <c r="AI45" s="67"/>
+      <c r="AJ45" s="67"/>
+      <c r="AK45" s="67"/>
+      <c r="AL45" s="67"/>
+      <c r="AM45" s="67"/>
+      <c r="AN45" s="67"/>
+      <c r="AO45" s="67"/>
+      <c r="AP45" s="67"/>
+      <c r="AQ45" s="67"/>
+      <c r="AR45" s="67"/>
+      <c r="AS45" s="67"/>
+      <c r="AT45" s="67"/>
+      <c r="AU45" s="67"/>
+      <c r="AV45" s="67"/>
+      <c r="AW45" s="67"/>
+      <c r="AX45" s="67"/>
+      <c r="AY45" s="67"/>
+      <c r="AZ45" s="67"/>
     </row>
     <row r="46" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="11"/>
       <c r="B46" s="11"/>
-      <c r="C46" s="64" t="s">
+      <c r="C46" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="D46" s="65"/>
-      <c r="E46" s="65"/>
-      <c r="F46" s="65"/>
-      <c r="G46" s="65"/>
-      <c r="H46" s="65"/>
-      <c r="I46" s="65"/>
-      <c r="J46" s="65"/>
-      <c r="K46" s="65"/>
-      <c r="L46" s="65"/>
-      <c r="M46" s="65"/>
-      <c r="N46" s="65"/>
-      <c r="O46" s="65"/>
-      <c r="P46" s="65"/>
-      <c r="Q46" s="65"/>
-      <c r="R46" s="65"/>
-      <c r="S46" s="65"/>
-      <c r="T46" s="65"/>
-      <c r="U46" s="65"/>
-      <c r="V46" s="65"/>
-      <c r="W46" s="65"/>
-      <c r="X46" s="65"/>
-      <c r="Y46" s="65"/>
-      <c r="Z46" s="65"/>
-      <c r="AA46" s="65"/>
-      <c r="AB46" s="65"/>
-      <c r="AC46" s="65"/>
-      <c r="AD46" s="65"/>
-      <c r="AE46" s="65"/>
-      <c r="AF46" s="65"/>
-      <c r="AG46" s="65"/>
-      <c r="AH46" s="65"/>
-      <c r="AI46" s="65"/>
-      <c r="AJ46" s="65"/>
-      <c r="AK46" s="65"/>
-      <c r="AL46" s="65"/>
-      <c r="AM46" s="65"/>
-      <c r="AN46" s="65"/>
-      <c r="AO46" s="65"/>
-      <c r="AP46" s="65"/>
-      <c r="AQ46" s="65"/>
-      <c r="AR46" s="65"/>
-      <c r="AS46" s="65"/>
-      <c r="AT46" s="65"/>
-      <c r="AU46" s="65"/>
-      <c r="AV46" s="65"/>
-      <c r="AW46" s="65"/>
-      <c r="AX46" s="65"/>
-      <c r="AY46" s="65"/>
-      <c r="AZ46" s="65"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="67"/>
+      <c r="F46" s="67"/>
+      <c r="G46" s="67"/>
+      <c r="H46" s="67"/>
+      <c r="I46" s="67"/>
+      <c r="J46" s="67"/>
+      <c r="K46" s="67"/>
+      <c r="L46" s="67"/>
+      <c r="M46" s="67"/>
+      <c r="N46" s="67"/>
+      <c r="O46" s="67"/>
+      <c r="P46" s="67"/>
+      <c r="Q46" s="67"/>
+      <c r="R46" s="67"/>
+      <c r="S46" s="67"/>
+      <c r="T46" s="67"/>
+      <c r="U46" s="67"/>
+      <c r="V46" s="67"/>
+      <c r="W46" s="67"/>
+      <c r="X46" s="67"/>
+      <c r="Y46" s="67"/>
+      <c r="Z46" s="67"/>
+      <c r="AA46" s="67"/>
+      <c r="AB46" s="67"/>
+      <c r="AC46" s="67"/>
+      <c r="AD46" s="67"/>
+      <c r="AE46" s="67"/>
+      <c r="AF46" s="67"/>
+      <c r="AG46" s="67"/>
+      <c r="AH46" s="67"/>
+      <c r="AI46" s="67"/>
+      <c r="AJ46" s="67"/>
+      <c r="AK46" s="67"/>
+      <c r="AL46" s="67"/>
+      <c r="AM46" s="67"/>
+      <c r="AN46" s="67"/>
+      <c r="AO46" s="67"/>
+      <c r="AP46" s="67"/>
+      <c r="AQ46" s="67"/>
+      <c r="AR46" s="67"/>
+      <c r="AS46" s="67"/>
+      <c r="AT46" s="67"/>
+      <c r="AU46" s="67"/>
+      <c r="AV46" s="67"/>
+      <c r="AW46" s="67"/>
+      <c r="AX46" s="67"/>
+      <c r="AY46" s="67"/>
+      <c r="AZ46" s="67"/>
     </row>
     <row r="47" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="11"/>
       <c r="B47" s="11"/>
-      <c r="C47" s="64" t="s">
+      <c r="C47" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="D47" s="65"/>
-      <c r="E47" s="65"/>
-      <c r="F47" s="65"/>
-      <c r="G47" s="65"/>
-      <c r="H47" s="65"/>
-      <c r="I47" s="65"/>
-      <c r="J47" s="65"/>
-      <c r="K47" s="65"/>
-      <c r="L47" s="65"/>
-      <c r="M47" s="65"/>
-      <c r="N47" s="65"/>
-      <c r="O47" s="65"/>
-      <c r="P47" s="65"/>
-      <c r="Q47" s="65"/>
-      <c r="R47" s="65"/>
-      <c r="S47" s="65"/>
-      <c r="T47" s="65"/>
-      <c r="U47" s="65"/>
-      <c r="V47" s="65"/>
-      <c r="W47" s="65"/>
-      <c r="X47" s="65"/>
-      <c r="Y47" s="65"/>
-      <c r="Z47" s="65"/>
-      <c r="AA47" s="65"/>
-      <c r="AB47" s="65"/>
-      <c r="AC47" s="65"/>
-      <c r="AD47" s="65"/>
-      <c r="AE47" s="65"/>
-      <c r="AF47" s="65"/>
-      <c r="AG47" s="65"/>
-      <c r="AH47" s="65"/>
-      <c r="AI47" s="65"/>
-      <c r="AJ47" s="65"/>
-      <c r="AK47" s="65"/>
-      <c r="AL47" s="65"/>
-      <c r="AM47" s="65"/>
-      <c r="AN47" s="65"/>
-      <c r="AO47" s="65"/>
-      <c r="AP47" s="65"/>
-      <c r="AQ47" s="65"/>
-      <c r="AR47" s="65"/>
-      <c r="AS47" s="65"/>
-      <c r="AT47" s="65"/>
-      <c r="AU47" s="65"/>
-      <c r="AV47" s="65"/>
-      <c r="AW47" s="65"/>
-      <c r="AX47" s="65"/>
-      <c r="AY47" s="65"/>
-      <c r="AZ47" s="65"/>
+      <c r="D47" s="67"/>
+      <c r="E47" s="67"/>
+      <c r="F47" s="67"/>
+      <c r="G47" s="67"/>
+      <c r="H47" s="67"/>
+      <c r="I47" s="67"/>
+      <c r="J47" s="67"/>
+      <c r="K47" s="67"/>
+      <c r="L47" s="67"/>
+      <c r="M47" s="67"/>
+      <c r="N47" s="67"/>
+      <c r="O47" s="67"/>
+      <c r="P47" s="67"/>
+      <c r="Q47" s="67"/>
+      <c r="R47" s="67"/>
+      <c r="S47" s="67"/>
+      <c r="T47" s="67"/>
+      <c r="U47" s="67"/>
+      <c r="V47" s="67"/>
+      <c r="W47" s="67"/>
+      <c r="X47" s="67"/>
+      <c r="Y47" s="67"/>
+      <c r="Z47" s="67"/>
+      <c r="AA47" s="67"/>
+      <c r="AB47" s="67"/>
+      <c r="AC47" s="67"/>
+      <c r="AD47" s="67"/>
+      <c r="AE47" s="67"/>
+      <c r="AF47" s="67"/>
+      <c r="AG47" s="67"/>
+      <c r="AH47" s="67"/>
+      <c r="AI47" s="67"/>
+      <c r="AJ47" s="67"/>
+      <c r="AK47" s="67"/>
+      <c r="AL47" s="67"/>
+      <c r="AM47" s="67"/>
+      <c r="AN47" s="67"/>
+      <c r="AO47" s="67"/>
+      <c r="AP47" s="67"/>
+      <c r="AQ47" s="67"/>
+      <c r="AR47" s="67"/>
+      <c r="AS47" s="67"/>
+      <c r="AT47" s="67"/>
+      <c r="AU47" s="67"/>
+      <c r="AV47" s="67"/>
+      <c r="AW47" s="67"/>
+      <c r="AX47" s="67"/>
+      <c r="AY47" s="67"/>
+      <c r="AZ47" s="67"/>
     </row>
     <row r="48" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="11"/>
       <c r="B48" s="11"/>
-      <c r="C48" s="68" t="s">
+      <c r="C48" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="D48" s="69"/>
-      <c r="E48" s="69"/>
-      <c r="F48" s="69"/>
-      <c r="G48" s="69"/>
-      <c r="H48" s="69"/>
-      <c r="I48" s="69"/>
-      <c r="J48" s="69"/>
-      <c r="K48" s="69"/>
-      <c r="L48" s="69"/>
-      <c r="M48" s="69"/>
-      <c r="N48" s="69"/>
-      <c r="O48" s="69"/>
-      <c r="P48" s="69"/>
-      <c r="Q48" s="69"/>
-      <c r="R48" s="69"/>
-      <c r="S48" s="69"/>
-      <c r="T48" s="69"/>
-      <c r="U48" s="69"/>
-      <c r="V48" s="69"/>
-      <c r="W48" s="69"/>
-      <c r="X48" s="69"/>
-      <c r="Y48" s="69"/>
-      <c r="Z48" s="69"/>
-      <c r="AA48" s="69"/>
-      <c r="AB48" s="69"/>
-      <c r="AC48" s="69"/>
-      <c r="AD48" s="69"/>
-      <c r="AE48" s="69"/>
-      <c r="AF48" s="69"/>
-      <c r="AG48" s="69"/>
-      <c r="AH48" s="69"/>
-      <c r="AI48" s="69"/>
-      <c r="AJ48" s="69"/>
-      <c r="AK48" s="69"/>
-      <c r="AL48" s="69"/>
-      <c r="AM48" s="69"/>
-      <c r="AN48" s="69"/>
-      <c r="AO48" s="69"/>
-      <c r="AP48" s="69"/>
-      <c r="AQ48" s="69"/>
-      <c r="AR48" s="69"/>
-      <c r="AS48" s="69"/>
-      <c r="AT48" s="69"/>
-      <c r="AU48" s="69"/>
-      <c r="AV48" s="69"/>
-      <c r="AW48" s="69"/>
-      <c r="AX48" s="69"/>
-      <c r="AY48" s="69"/>
-      <c r="AZ48" s="69"/>
+      <c r="D48" s="71"/>
+      <c r="E48" s="71"/>
+      <c r="F48" s="71"/>
+      <c r="G48" s="71"/>
+      <c r="H48" s="71"/>
+      <c r="I48" s="71"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="71"/>
+      <c r="L48" s="71"/>
+      <c r="M48" s="71"/>
+      <c r="N48" s="71"/>
+      <c r="O48" s="71"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="71"/>
+      <c r="S48" s="71"/>
+      <c r="T48" s="71"/>
+      <c r="U48" s="71"/>
+      <c r="V48" s="71"/>
+      <c r="W48" s="71"/>
+      <c r="X48" s="71"/>
+      <c r="Y48" s="71"/>
+      <c r="Z48" s="71"/>
+      <c r="AA48" s="71"/>
+      <c r="AB48" s="71"/>
+      <c r="AC48" s="71"/>
+      <c r="AD48" s="71"/>
+      <c r="AE48" s="71"/>
+      <c r="AF48" s="71"/>
+      <c r="AG48" s="71"/>
+      <c r="AH48" s="71"/>
+      <c r="AI48" s="71"/>
+      <c r="AJ48" s="71"/>
+      <c r="AK48" s="71"/>
+      <c r="AL48" s="71"/>
+      <c r="AM48" s="71"/>
+      <c r="AN48" s="71"/>
+      <c r="AO48" s="71"/>
+      <c r="AP48" s="71"/>
+      <c r="AQ48" s="71"/>
+      <c r="AR48" s="71"/>
+      <c r="AS48" s="71"/>
+      <c r="AT48" s="71"/>
+      <c r="AU48" s="71"/>
+      <c r="AV48" s="71"/>
+      <c r="AW48" s="71"/>
+      <c r="AX48" s="71"/>
+      <c r="AY48" s="71"/>
+      <c r="AZ48" s="71"/>
     </row>
     <row r="49" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="11"/>
       <c r="B49" s="11"/>
-      <c r="C49" s="64" t="s">
+      <c r="C49" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="D49" s="65"/>
-      <c r="E49" s="65"/>
-      <c r="F49" s="65"/>
-      <c r="G49" s="65"/>
-      <c r="H49" s="65"/>
-      <c r="I49" s="65"/>
-      <c r="J49" s="65"/>
-      <c r="K49" s="65"/>
-      <c r="L49" s="65"/>
-      <c r="M49" s="65"/>
-      <c r="N49" s="65"/>
-      <c r="O49" s="65"/>
-      <c r="P49" s="65"/>
-      <c r="Q49" s="65"/>
-      <c r="R49" s="65"/>
-      <c r="S49" s="65"/>
-      <c r="T49" s="65"/>
-      <c r="U49" s="65"/>
-      <c r="V49" s="65"/>
-      <c r="W49" s="65"/>
-      <c r="X49" s="65"/>
-      <c r="Y49" s="65"/>
-      <c r="Z49" s="65"/>
-      <c r="AA49" s="65"/>
-      <c r="AB49" s="65"/>
-      <c r="AC49" s="65"/>
-      <c r="AD49" s="65"/>
-      <c r="AE49" s="65"/>
-      <c r="AF49" s="65"/>
-      <c r="AG49" s="65"/>
-      <c r="AH49" s="65"/>
-      <c r="AI49" s="65"/>
-      <c r="AJ49" s="65"/>
-      <c r="AK49" s="65"/>
-      <c r="AL49" s="65"/>
-      <c r="AM49" s="65"/>
-      <c r="AN49" s="65"/>
-      <c r="AO49" s="65"/>
-      <c r="AP49" s="65"/>
-      <c r="AQ49" s="65"/>
-      <c r="AR49" s="65"/>
-      <c r="AS49" s="65"/>
-      <c r="AT49" s="65"/>
-      <c r="AU49" s="65"/>
-      <c r="AV49" s="65"/>
-      <c r="AW49" s="65"/>
-      <c r="AX49" s="65"/>
-      <c r="AY49" s="65"/>
-      <c r="AZ49" s="65"/>
+      <c r="D49" s="67"/>
+      <c r="E49" s="67"/>
+      <c r="F49" s="67"/>
+      <c r="G49" s="67"/>
+      <c r="H49" s="67"/>
+      <c r="I49" s="67"/>
+      <c r="J49" s="67"/>
+      <c r="K49" s="67"/>
+      <c r="L49" s="67"/>
+      <c r="M49" s="67"/>
+      <c r="N49" s="67"/>
+      <c r="O49" s="67"/>
+      <c r="P49" s="67"/>
+      <c r="Q49" s="67"/>
+      <c r="R49" s="67"/>
+      <c r="S49" s="67"/>
+      <c r="T49" s="67"/>
+      <c r="U49" s="67"/>
+      <c r="V49" s="67"/>
+      <c r="W49" s="67"/>
+      <c r="X49" s="67"/>
+      <c r="Y49" s="67"/>
+      <c r="Z49" s="67"/>
+      <c r="AA49" s="67"/>
+      <c r="AB49" s="67"/>
+      <c r="AC49" s="67"/>
+      <c r="AD49" s="67"/>
+      <c r="AE49" s="67"/>
+      <c r="AF49" s="67"/>
+      <c r="AG49" s="67"/>
+      <c r="AH49" s="67"/>
+      <c r="AI49" s="67"/>
+      <c r="AJ49" s="67"/>
+      <c r="AK49" s="67"/>
+      <c r="AL49" s="67"/>
+      <c r="AM49" s="67"/>
+      <c r="AN49" s="67"/>
+      <c r="AO49" s="67"/>
+      <c r="AP49" s="67"/>
+      <c r="AQ49" s="67"/>
+      <c r="AR49" s="67"/>
+      <c r="AS49" s="67"/>
+      <c r="AT49" s="67"/>
+      <c r="AU49" s="67"/>
+      <c r="AV49" s="67"/>
+      <c r="AW49" s="67"/>
+      <c r="AX49" s="67"/>
+      <c r="AY49" s="67"/>
+      <c r="AZ49" s="67"/>
     </row>
     <row r="50" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="11"/>
       <c r="B50" s="11"/>
-      <c r="C50" s="64" t="s">
+      <c r="C50" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="D50" s="65"/>
-      <c r="E50" s="65"/>
-      <c r="F50" s="65"/>
-      <c r="G50" s="65"/>
-      <c r="H50" s="65"/>
-      <c r="I50" s="65"/>
-      <c r="J50" s="65"/>
-      <c r="K50" s="65"/>
-      <c r="L50" s="65"/>
-      <c r="M50" s="65"/>
-      <c r="N50" s="65"/>
-      <c r="O50" s="65"/>
-      <c r="P50" s="65"/>
-      <c r="Q50" s="65"/>
-      <c r="R50" s="65"/>
-      <c r="S50" s="65"/>
-      <c r="T50" s="65"/>
-      <c r="U50" s="65"/>
-      <c r="V50" s="65"/>
-      <c r="W50" s="65"/>
-      <c r="X50" s="65"/>
-      <c r="Y50" s="65"/>
-      <c r="Z50" s="65"/>
-      <c r="AA50" s="65"/>
-      <c r="AB50" s="65"/>
-      <c r="AC50" s="65"/>
-      <c r="AD50" s="65"/>
-      <c r="AE50" s="65"/>
-      <c r="AF50" s="65"/>
-      <c r="AG50" s="65"/>
-      <c r="AH50" s="65"/>
-      <c r="AI50" s="65"/>
-      <c r="AJ50" s="65"/>
-      <c r="AK50" s="65"/>
-      <c r="AL50" s="65"/>
-      <c r="AM50" s="65"/>
-      <c r="AN50" s="65"/>
-      <c r="AO50" s="65"/>
-      <c r="AP50" s="65"/>
-      <c r="AQ50" s="65"/>
-      <c r="AR50" s="65"/>
-      <c r="AS50" s="65"/>
-      <c r="AT50" s="65"/>
-      <c r="AU50" s="65"/>
-      <c r="AV50" s="65"/>
-      <c r="AW50" s="65"/>
-      <c r="AX50" s="65"/>
-      <c r="AY50" s="65"/>
-      <c r="AZ50" s="65"/>
+      <c r="D50" s="67"/>
+      <c r="E50" s="67"/>
+      <c r="F50" s="67"/>
+      <c r="G50" s="67"/>
+      <c r="H50" s="67"/>
+      <c r="I50" s="67"/>
+      <c r="J50" s="67"/>
+      <c r="K50" s="67"/>
+      <c r="L50" s="67"/>
+      <c r="M50" s="67"/>
+      <c r="N50" s="67"/>
+      <c r="O50" s="67"/>
+      <c r="P50" s="67"/>
+      <c r="Q50" s="67"/>
+      <c r="R50" s="67"/>
+      <c r="S50" s="67"/>
+      <c r="T50" s="67"/>
+      <c r="U50" s="67"/>
+      <c r="V50" s="67"/>
+      <c r="W50" s="67"/>
+      <c r="X50" s="67"/>
+      <c r="Y50" s="67"/>
+      <c r="Z50" s="67"/>
+      <c r="AA50" s="67"/>
+      <c r="AB50" s="67"/>
+      <c r="AC50" s="67"/>
+      <c r="AD50" s="67"/>
+      <c r="AE50" s="67"/>
+      <c r="AF50" s="67"/>
+      <c r="AG50" s="67"/>
+      <c r="AH50" s="67"/>
+      <c r="AI50" s="67"/>
+      <c r="AJ50" s="67"/>
+      <c r="AK50" s="67"/>
+      <c r="AL50" s="67"/>
+      <c r="AM50" s="67"/>
+      <c r="AN50" s="67"/>
+      <c r="AO50" s="67"/>
+      <c r="AP50" s="67"/>
+      <c r="AQ50" s="67"/>
+      <c r="AR50" s="67"/>
+      <c r="AS50" s="67"/>
+      <c r="AT50" s="67"/>
+      <c r="AU50" s="67"/>
+      <c r="AV50" s="67"/>
+      <c r="AW50" s="67"/>
+      <c r="AX50" s="67"/>
+      <c r="AY50" s="67"/>
+      <c r="AZ50" s="67"/>
     </row>
     <row r="51" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="11"/>
       <c r="B51" s="11"/>
-      <c r="C51" s="64" t="s">
+      <c r="C51" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="D51" s="65"/>
-      <c r="E51" s="65"/>
-      <c r="F51" s="65"/>
-      <c r="G51" s="65"/>
-      <c r="H51" s="65"/>
-      <c r="I51" s="65"/>
-      <c r="J51" s="65"/>
-      <c r="K51" s="65"/>
-      <c r="L51" s="65"/>
-      <c r="M51" s="65"/>
-      <c r="N51" s="65"/>
-      <c r="O51" s="65"/>
-      <c r="P51" s="65"/>
-      <c r="Q51" s="65"/>
-      <c r="R51" s="65"/>
-      <c r="S51" s="65"/>
-      <c r="T51" s="65"/>
-      <c r="U51" s="65"/>
-      <c r="V51" s="65"/>
-      <c r="W51" s="65"/>
-      <c r="X51" s="65"/>
-      <c r="Y51" s="65"/>
-      <c r="Z51" s="65"/>
-      <c r="AA51" s="65"/>
-      <c r="AB51" s="65"/>
-      <c r="AC51" s="65"/>
-      <c r="AD51" s="65"/>
-      <c r="AE51" s="65"/>
-      <c r="AF51" s="65"/>
-      <c r="AG51" s="65"/>
-      <c r="AH51" s="65"/>
-      <c r="AI51" s="65"/>
-      <c r="AJ51" s="65"/>
-      <c r="AK51" s="65"/>
-      <c r="AL51" s="65"/>
-      <c r="AM51" s="65"/>
-      <c r="AN51" s="65"/>
-      <c r="AO51" s="65"/>
-      <c r="AP51" s="65"/>
-      <c r="AQ51" s="65"/>
-      <c r="AR51" s="65"/>
-      <c r="AS51" s="65"/>
-      <c r="AT51" s="65"/>
-      <c r="AU51" s="65"/>
-      <c r="AV51" s="65"/>
-      <c r="AW51" s="65"/>
-      <c r="AX51" s="65"/>
-      <c r="AY51" s="65"/>
-      <c r="AZ51" s="65"/>
+      <c r="D51" s="67"/>
+      <c r="E51" s="67"/>
+      <c r="F51" s="67"/>
+      <c r="G51" s="67"/>
+      <c r="H51" s="67"/>
+      <c r="I51" s="67"/>
+      <c r="J51" s="67"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="67"/>
+      <c r="M51" s="67"/>
+      <c r="N51" s="67"/>
+      <c r="O51" s="67"/>
+      <c r="P51" s="67"/>
+      <c r="Q51" s="67"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="67"/>
+      <c r="T51" s="67"/>
+      <c r="U51" s="67"/>
+      <c r="V51" s="67"/>
+      <c r="W51" s="67"/>
+      <c r="X51" s="67"/>
+      <c r="Y51" s="67"/>
+      <c r="Z51" s="67"/>
+      <c r="AA51" s="67"/>
+      <c r="AB51" s="67"/>
+      <c r="AC51" s="67"/>
+      <c r="AD51" s="67"/>
+      <c r="AE51" s="67"/>
+      <c r="AF51" s="67"/>
+      <c r="AG51" s="67"/>
+      <c r="AH51" s="67"/>
+      <c r="AI51" s="67"/>
+      <c r="AJ51" s="67"/>
+      <c r="AK51" s="67"/>
+      <c r="AL51" s="67"/>
+      <c r="AM51" s="67"/>
+      <c r="AN51" s="67"/>
+      <c r="AO51" s="67"/>
+      <c r="AP51" s="67"/>
+      <c r="AQ51" s="67"/>
+      <c r="AR51" s="67"/>
+      <c r="AS51" s="67"/>
+      <c r="AT51" s="67"/>
+      <c r="AU51" s="67"/>
+      <c r="AV51" s="67"/>
+      <c r="AW51" s="67"/>
+      <c r="AX51" s="67"/>
+      <c r="AY51" s="67"/>
+      <c r="AZ51" s="67"/>
     </row>
     <row r="52" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="14"/>
       <c r="B52" s="11"/>
-      <c r="C52" s="64" t="s">
+      <c r="C52" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="D52" s="65"/>
-      <c r="E52" s="65"/>
-      <c r="F52" s="65"/>
-      <c r="G52" s="65"/>
-      <c r="H52" s="65"/>
-      <c r="I52" s="65"/>
-      <c r="J52" s="65"/>
-      <c r="K52" s="65"/>
-      <c r="L52" s="65"/>
-      <c r="M52" s="65"/>
-      <c r="N52" s="65"/>
-      <c r="O52" s="65"/>
-      <c r="P52" s="65"/>
-      <c r="Q52" s="65"/>
-      <c r="R52" s="65"/>
-      <c r="S52" s="65"/>
-      <c r="T52" s="65"/>
-      <c r="U52" s="65"/>
-      <c r="V52" s="65"/>
-      <c r="W52" s="65"/>
-      <c r="X52" s="65"/>
-      <c r="Y52" s="65"/>
-      <c r="Z52" s="65"/>
-      <c r="AA52" s="65"/>
-      <c r="AB52" s="65"/>
-      <c r="AC52" s="65"/>
-      <c r="AD52" s="65"/>
-      <c r="AE52" s="65"/>
-      <c r="AF52" s="65"/>
-      <c r="AG52" s="65"/>
-      <c r="AH52" s="65"/>
-      <c r="AI52" s="65"/>
-      <c r="AJ52" s="65"/>
-      <c r="AK52" s="65"/>
-      <c r="AL52" s="65"/>
-      <c r="AM52" s="65"/>
-      <c r="AN52" s="65"/>
-      <c r="AO52" s="65"/>
-      <c r="AP52" s="65"/>
-      <c r="AQ52" s="65"/>
-      <c r="AR52" s="65"/>
-      <c r="AS52" s="65"/>
-      <c r="AT52" s="65"/>
-      <c r="AU52" s="65"/>
-      <c r="AV52" s="65"/>
-      <c r="AW52" s="65"/>
-      <c r="AX52" s="65"/>
-      <c r="AY52" s="65"/>
-      <c r="AZ52" s="65"/>
+      <c r="D52" s="67"/>
+      <c r="E52" s="67"/>
+      <c r="F52" s="67"/>
+      <c r="G52" s="67"/>
+      <c r="H52" s="67"/>
+      <c r="I52" s="67"/>
+      <c r="J52" s="67"/>
+      <c r="K52" s="67"/>
+      <c r="L52" s="67"/>
+      <c r="M52" s="67"/>
+      <c r="N52" s="67"/>
+      <c r="O52" s="67"/>
+      <c r="P52" s="67"/>
+      <c r="Q52" s="67"/>
+      <c r="R52" s="67"/>
+      <c r="S52" s="67"/>
+      <c r="T52" s="67"/>
+      <c r="U52" s="67"/>
+      <c r="V52" s="67"/>
+      <c r="W52" s="67"/>
+      <c r="X52" s="67"/>
+      <c r="Y52" s="67"/>
+      <c r="Z52" s="67"/>
+      <c r="AA52" s="67"/>
+      <c r="AB52" s="67"/>
+      <c r="AC52" s="67"/>
+      <c r="AD52" s="67"/>
+      <c r="AE52" s="67"/>
+      <c r="AF52" s="67"/>
+      <c r="AG52" s="67"/>
+      <c r="AH52" s="67"/>
+      <c r="AI52" s="67"/>
+      <c r="AJ52" s="67"/>
+      <c r="AK52" s="67"/>
+      <c r="AL52" s="67"/>
+      <c r="AM52" s="67"/>
+      <c r="AN52" s="67"/>
+      <c r="AO52" s="67"/>
+      <c r="AP52" s="67"/>
+      <c r="AQ52" s="67"/>
+      <c r="AR52" s="67"/>
+      <c r="AS52" s="67"/>
+      <c r="AT52" s="67"/>
+      <c r="AU52" s="67"/>
+      <c r="AV52" s="67"/>
+      <c r="AW52" s="67"/>
+      <c r="AX52" s="67"/>
+      <c r="AY52" s="67"/>
+      <c r="AZ52" s="67"/>
     </row>
     <row r="53" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="11"/>
       <c r="B53" s="11"/>
-      <c r="C53" s="64" t="s">
+      <c r="C53" s="68" t="s">
         <v>30</v>
       </c>
-      <c r="D53" s="65"/>
-      <c r="E53" s="65"/>
-      <c r="F53" s="65"/>
-      <c r="G53" s="65"/>
-      <c r="H53" s="65"/>
-      <c r="I53" s="65"/>
-      <c r="J53" s="65"/>
-      <c r="K53" s="65"/>
-      <c r="L53" s="65"/>
-      <c r="M53" s="65"/>
-      <c r="N53" s="65"/>
-      <c r="O53" s="65"/>
-      <c r="P53" s="65"/>
-      <c r="Q53" s="65"/>
-      <c r="R53" s="65"/>
-      <c r="S53" s="65"/>
-      <c r="T53" s="65"/>
-      <c r="U53" s="65"/>
-      <c r="V53" s="65"/>
-      <c r="W53" s="65"/>
-      <c r="X53" s="65"/>
-      <c r="Y53" s="65"/>
-      <c r="Z53" s="65"/>
-      <c r="AA53" s="65"/>
-      <c r="AB53" s="65"/>
-      <c r="AC53" s="65"/>
-      <c r="AD53" s="65"/>
-      <c r="AE53" s="65"/>
-      <c r="AF53" s="65"/>
-      <c r="AG53" s="65"/>
-      <c r="AH53" s="65"/>
-      <c r="AI53" s="65"/>
-      <c r="AJ53" s="65"/>
-      <c r="AK53" s="65"/>
-      <c r="AL53" s="65"/>
-      <c r="AM53" s="65"/>
-      <c r="AN53" s="65"/>
-      <c r="AO53" s="65"/>
-      <c r="AP53" s="65"/>
-      <c r="AQ53" s="65"/>
-      <c r="AR53" s="65"/>
-      <c r="AS53" s="65"/>
-      <c r="AT53" s="65"/>
-      <c r="AU53" s="65"/>
-      <c r="AV53" s="65"/>
-      <c r="AW53" s="65"/>
-      <c r="AX53" s="65"/>
-      <c r="AY53" s="65"/>
-      <c r="AZ53" s="65"/>
+      <c r="D53" s="67"/>
+      <c r="E53" s="67"/>
+      <c r="F53" s="67"/>
+      <c r="G53" s="67"/>
+      <c r="H53" s="67"/>
+      <c r="I53" s="67"/>
+      <c r="J53" s="67"/>
+      <c r="K53" s="67"/>
+      <c r="L53" s="67"/>
+      <c r="M53" s="67"/>
+      <c r="N53" s="67"/>
+      <c r="O53" s="67"/>
+      <c r="P53" s="67"/>
+      <c r="Q53" s="67"/>
+      <c r="R53" s="67"/>
+      <c r="S53" s="67"/>
+      <c r="T53" s="67"/>
+      <c r="U53" s="67"/>
+      <c r="V53" s="67"/>
+      <c r="W53" s="67"/>
+      <c r="X53" s="67"/>
+      <c r="Y53" s="67"/>
+      <c r="Z53" s="67"/>
+      <c r="AA53" s="67"/>
+      <c r="AB53" s="67"/>
+      <c r="AC53" s="67"/>
+      <c r="AD53" s="67"/>
+      <c r="AE53" s="67"/>
+      <c r="AF53" s="67"/>
+      <c r="AG53" s="67"/>
+      <c r="AH53" s="67"/>
+      <c r="AI53" s="67"/>
+      <c r="AJ53" s="67"/>
+      <c r="AK53" s="67"/>
+      <c r="AL53" s="67"/>
+      <c r="AM53" s="67"/>
+      <c r="AN53" s="67"/>
+      <c r="AO53" s="67"/>
+      <c r="AP53" s="67"/>
+      <c r="AQ53" s="67"/>
+      <c r="AR53" s="67"/>
+      <c r="AS53" s="67"/>
+      <c r="AT53" s="67"/>
+      <c r="AU53" s="67"/>
+      <c r="AV53" s="67"/>
+      <c r="AW53" s="67"/>
+      <c r="AX53" s="67"/>
+      <c r="AY53" s="67"/>
+      <c r="AZ53" s="67"/>
     </row>
     <row r="54" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="11"/>
       <c r="B54" s="11"/>
-      <c r="C54" s="64" t="s">
+      <c r="C54" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="D54" s="65"/>
-      <c r="E54" s="65"/>
-      <c r="F54" s="65"/>
-      <c r="G54" s="65"/>
-      <c r="H54" s="65"/>
-      <c r="I54" s="65"/>
-      <c r="J54" s="65"/>
-      <c r="K54" s="65"/>
-      <c r="L54" s="65"/>
-      <c r="M54" s="65"/>
-      <c r="N54" s="65"/>
-      <c r="O54" s="65"/>
-      <c r="P54" s="65"/>
-      <c r="Q54" s="65"/>
-      <c r="R54" s="65"/>
-      <c r="S54" s="65"/>
-      <c r="T54" s="65"/>
-      <c r="U54" s="65"/>
-      <c r="V54" s="65"/>
-      <c r="W54" s="65"/>
-      <c r="X54" s="65"/>
-      <c r="Y54" s="65"/>
-      <c r="Z54" s="65"/>
-      <c r="AA54" s="65"/>
-      <c r="AB54" s="65"/>
-      <c r="AC54" s="65"/>
-      <c r="AD54" s="65"/>
-      <c r="AE54" s="65"/>
-      <c r="AF54" s="65"/>
-      <c r="AG54" s="65"/>
-      <c r="AH54" s="65"/>
-      <c r="AI54" s="65"/>
-      <c r="AJ54" s="65"/>
-      <c r="AK54" s="65"/>
-      <c r="AL54" s="65"/>
-      <c r="AM54" s="65"/>
-      <c r="AN54" s="65"/>
-      <c r="AO54" s="65"/>
-      <c r="AP54" s="65"/>
-      <c r="AQ54" s="65"/>
-      <c r="AR54" s="65"/>
-      <c r="AS54" s="65"/>
-      <c r="AT54" s="65"/>
-      <c r="AU54" s="65"/>
-      <c r="AV54" s="65"/>
-      <c r="AW54" s="65"/>
-      <c r="AX54" s="65"/>
-      <c r="AY54" s="65"/>
-      <c r="AZ54" s="65"/>
+      <c r="D54" s="67"/>
+      <c r="E54" s="67"/>
+      <c r="F54" s="67"/>
+      <c r="G54" s="67"/>
+      <c r="H54" s="67"/>
+      <c r="I54" s="67"/>
+      <c r="J54" s="67"/>
+      <c r="K54" s="67"/>
+      <c r="L54" s="67"/>
+      <c r="M54" s="67"/>
+      <c r="N54" s="67"/>
+      <c r="O54" s="67"/>
+      <c r="P54" s="67"/>
+      <c r="Q54" s="67"/>
+      <c r="R54" s="67"/>
+      <c r="S54" s="67"/>
+      <c r="T54" s="67"/>
+      <c r="U54" s="67"/>
+      <c r="V54" s="67"/>
+      <c r="W54" s="67"/>
+      <c r="X54" s="67"/>
+      <c r="Y54" s="67"/>
+      <c r="Z54" s="67"/>
+      <c r="AA54" s="67"/>
+      <c r="AB54" s="67"/>
+      <c r="AC54" s="67"/>
+      <c r="AD54" s="67"/>
+      <c r="AE54" s="67"/>
+      <c r="AF54" s="67"/>
+      <c r="AG54" s="67"/>
+      <c r="AH54" s="67"/>
+      <c r="AI54" s="67"/>
+      <c r="AJ54" s="67"/>
+      <c r="AK54" s="67"/>
+      <c r="AL54" s="67"/>
+      <c r="AM54" s="67"/>
+      <c r="AN54" s="67"/>
+      <c r="AO54" s="67"/>
+      <c r="AP54" s="67"/>
+      <c r="AQ54" s="67"/>
+      <c r="AR54" s="67"/>
+      <c r="AS54" s="67"/>
+      <c r="AT54" s="67"/>
+      <c r="AU54" s="67"/>
+      <c r="AV54" s="67"/>
+      <c r="AW54" s="67"/>
+      <c r="AX54" s="67"/>
+      <c r="AY54" s="67"/>
+      <c r="AZ54" s="67"/>
     </row>
     <row r="55" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="11"/>
       <c r="B55" s="11"/>
-      <c r="C55" s="64" t="s">
+      <c r="C55" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="D55" s="65"/>
-      <c r="E55" s="65"/>
-      <c r="F55" s="65"/>
-      <c r="G55" s="65"/>
-      <c r="H55" s="65"/>
-      <c r="I55" s="65"/>
-      <c r="J55" s="65"/>
-      <c r="K55" s="65"/>
-      <c r="L55" s="65"/>
-      <c r="M55" s="65"/>
-      <c r="N55" s="65"/>
-      <c r="O55" s="65"/>
-      <c r="P55" s="65"/>
-      <c r="Q55" s="65"/>
-      <c r="R55" s="65"/>
-      <c r="S55" s="65"/>
-      <c r="T55" s="65"/>
-      <c r="U55" s="65"/>
-      <c r="V55" s="65"/>
-      <c r="W55" s="65"/>
-      <c r="X55" s="65"/>
-      <c r="Y55" s="65"/>
-      <c r="Z55" s="65"/>
-      <c r="AA55" s="65"/>
-      <c r="AB55" s="65"/>
-      <c r="AC55" s="65"/>
-      <c r="AD55" s="65"/>
-      <c r="AE55" s="65"/>
-      <c r="AF55" s="65"/>
-      <c r="AG55" s="65"/>
-      <c r="AH55" s="65"/>
-      <c r="AI55" s="65"/>
-      <c r="AJ55" s="65"/>
-      <c r="AK55" s="65"/>
-      <c r="AL55" s="65"/>
-      <c r="AM55" s="65"/>
-      <c r="AN55" s="65"/>
-      <c r="AO55" s="65"/>
-      <c r="AP55" s="65"/>
-      <c r="AQ55" s="65"/>
-      <c r="AR55" s="65"/>
-      <c r="AS55" s="65"/>
-      <c r="AT55" s="65"/>
-      <c r="AU55" s="65"/>
-      <c r="AV55" s="65"/>
-      <c r="AW55" s="65"/>
-      <c r="AX55" s="65"/>
-      <c r="AY55" s="65"/>
-      <c r="AZ55" s="65"/>
+      <c r="D55" s="67"/>
+      <c r="E55" s="67"/>
+      <c r="F55" s="67"/>
+      <c r="G55" s="67"/>
+      <c r="H55" s="67"/>
+      <c r="I55" s="67"/>
+      <c r="J55" s="67"/>
+      <c r="K55" s="67"/>
+      <c r="L55" s="67"/>
+      <c r="M55" s="67"/>
+      <c r="N55" s="67"/>
+      <c r="O55" s="67"/>
+      <c r="P55" s="67"/>
+      <c r="Q55" s="67"/>
+      <c r="R55" s="67"/>
+      <c r="S55" s="67"/>
+      <c r="T55" s="67"/>
+      <c r="U55" s="67"/>
+      <c r="V55" s="67"/>
+      <c r="W55" s="67"/>
+      <c r="X55" s="67"/>
+      <c r="Y55" s="67"/>
+      <c r="Z55" s="67"/>
+      <c r="AA55" s="67"/>
+      <c r="AB55" s="67"/>
+      <c r="AC55" s="67"/>
+      <c r="AD55" s="67"/>
+      <c r="AE55" s="67"/>
+      <c r="AF55" s="67"/>
+      <c r="AG55" s="67"/>
+      <c r="AH55" s="67"/>
+      <c r="AI55" s="67"/>
+      <c r="AJ55" s="67"/>
+      <c r="AK55" s="67"/>
+      <c r="AL55" s="67"/>
+      <c r="AM55" s="67"/>
+      <c r="AN55" s="67"/>
+      <c r="AO55" s="67"/>
+      <c r="AP55" s="67"/>
+      <c r="AQ55" s="67"/>
+      <c r="AR55" s="67"/>
+      <c r="AS55" s="67"/>
+      <c r="AT55" s="67"/>
+      <c r="AU55" s="67"/>
+      <c r="AV55" s="67"/>
+      <c r="AW55" s="67"/>
+      <c r="AX55" s="67"/>
+      <c r="AY55" s="67"/>
+      <c r="AZ55" s="67"/>
     </row>
     <row r="56" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="11"/>
       <c r="B56" s="11"/>
-      <c r="C56" s="64" t="s">
+      <c r="C56" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="D56" s="65"/>
-      <c r="E56" s="65"/>
-      <c r="F56" s="65"/>
-      <c r="G56" s="65"/>
-      <c r="H56" s="65"/>
-      <c r="I56" s="65"/>
-      <c r="J56" s="65"/>
-      <c r="K56" s="65"/>
-      <c r="L56" s="65"/>
-      <c r="M56" s="65"/>
-      <c r="N56" s="65"/>
-      <c r="O56" s="65"/>
-      <c r="P56" s="65"/>
-      <c r="Q56" s="65"/>
-      <c r="R56" s="65"/>
-      <c r="S56" s="65"/>
-      <c r="T56" s="65"/>
-      <c r="U56" s="65"/>
-      <c r="V56" s="65"/>
-      <c r="W56" s="65"/>
-      <c r="X56" s="65"/>
-      <c r="Y56" s="65"/>
-      <c r="Z56" s="65"/>
-      <c r="AA56" s="65"/>
-      <c r="AB56" s="65"/>
-      <c r="AC56" s="65"/>
-      <c r="AD56" s="65"/>
-      <c r="AE56" s="65"/>
-      <c r="AF56" s="65"/>
-      <c r="AG56" s="65"/>
-      <c r="AH56" s="65"/>
-      <c r="AI56" s="65"/>
-      <c r="AJ56" s="65"/>
-      <c r="AK56" s="65"/>
-      <c r="AL56" s="65"/>
-      <c r="AM56" s="65"/>
-      <c r="AN56" s="65"/>
-      <c r="AO56" s="65"/>
-      <c r="AP56" s="65"/>
-      <c r="AQ56" s="65"/>
-      <c r="AR56" s="65"/>
-      <c r="AS56" s="65"/>
-      <c r="AT56" s="65"/>
-      <c r="AU56" s="65"/>
-      <c r="AV56" s="65"/>
-      <c r="AW56" s="65"/>
-      <c r="AX56" s="65"/>
-      <c r="AY56" s="65"/>
-      <c r="AZ56" s="65"/>
+      <c r="D56" s="67"/>
+      <c r="E56" s="67"/>
+      <c r="F56" s="67"/>
+      <c r="G56" s="67"/>
+      <c r="H56" s="67"/>
+      <c r="I56" s="67"/>
+      <c r="J56" s="67"/>
+      <c r="K56" s="67"/>
+      <c r="L56" s="67"/>
+      <c r="M56" s="67"/>
+      <c r="N56" s="67"/>
+      <c r="O56" s="67"/>
+      <c r="P56" s="67"/>
+      <c r="Q56" s="67"/>
+      <c r="R56" s="67"/>
+      <c r="S56" s="67"/>
+      <c r="T56" s="67"/>
+      <c r="U56" s="67"/>
+      <c r="V56" s="67"/>
+      <c r="W56" s="67"/>
+      <c r="X56" s="67"/>
+      <c r="Y56" s="67"/>
+      <c r="Z56" s="67"/>
+      <c r="AA56" s="67"/>
+      <c r="AB56" s="67"/>
+      <c r="AC56" s="67"/>
+      <c r="AD56" s="67"/>
+      <c r="AE56" s="67"/>
+      <c r="AF56" s="67"/>
+      <c r="AG56" s="67"/>
+      <c r="AH56" s="67"/>
+      <c r="AI56" s="67"/>
+      <c r="AJ56" s="67"/>
+      <c r="AK56" s="67"/>
+      <c r="AL56" s="67"/>
+      <c r="AM56" s="67"/>
+      <c r="AN56" s="67"/>
+      <c r="AO56" s="67"/>
+      <c r="AP56" s="67"/>
+      <c r="AQ56" s="67"/>
+      <c r="AR56" s="67"/>
+      <c r="AS56" s="67"/>
+      <c r="AT56" s="67"/>
+      <c r="AU56" s="67"/>
+      <c r="AV56" s="67"/>
+      <c r="AW56" s="67"/>
+      <c r="AX56" s="67"/>
+      <c r="AY56" s="67"/>
+      <c r="AZ56" s="67"/>
     </row>
     <row r="57" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="11"/>
       <c r="B57" s="11"/>
-      <c r="C57" s="64" t="s">
+      <c r="C57" s="68" t="s">
         <v>34</v>
       </c>
-      <c r="D57" s="65"/>
-      <c r="E57" s="65"/>
-      <c r="F57" s="65"/>
-      <c r="G57" s="65"/>
-      <c r="H57" s="65"/>
-      <c r="I57" s="65"/>
-      <c r="J57" s="65"/>
-      <c r="K57" s="65"/>
-      <c r="L57" s="65"/>
-      <c r="M57" s="65"/>
-      <c r="N57" s="65"/>
-      <c r="O57" s="65"/>
-      <c r="P57" s="65"/>
-      <c r="Q57" s="65"/>
-      <c r="R57" s="65"/>
-      <c r="S57" s="65"/>
-      <c r="T57" s="65"/>
-      <c r="U57" s="65"/>
-      <c r="V57" s="65"/>
-      <c r="W57" s="65"/>
-      <c r="X57" s="65"/>
-      <c r="Y57" s="65"/>
-      <c r="Z57" s="65"/>
-      <c r="AA57" s="65"/>
-      <c r="AB57" s="65"/>
-      <c r="AC57" s="65"/>
-      <c r="AD57" s="65"/>
-      <c r="AE57" s="65"/>
-      <c r="AF57" s="65"/>
-      <c r="AG57" s="65"/>
-      <c r="AH57" s="65"/>
-      <c r="AI57" s="65"/>
-      <c r="AJ57" s="65"/>
-      <c r="AK57" s="65"/>
-      <c r="AL57" s="65"/>
-      <c r="AM57" s="65"/>
-      <c r="AN57" s="65"/>
-      <c r="AO57" s="65"/>
-      <c r="AP57" s="65"/>
-      <c r="AQ57" s="65"/>
-      <c r="AR57" s="65"/>
-      <c r="AS57" s="65"/>
-      <c r="AT57" s="65"/>
-      <c r="AU57" s="65"/>
-      <c r="AV57" s="65"/>
-      <c r="AW57" s="65"/>
-      <c r="AX57" s="65"/>
-      <c r="AY57" s="65"/>
-      <c r="AZ57" s="65"/>
+      <c r="D57" s="67"/>
+      <c r="E57" s="67"/>
+      <c r="F57" s="67"/>
+      <c r="G57" s="67"/>
+      <c r="H57" s="67"/>
+      <c r="I57" s="67"/>
+      <c r="J57" s="67"/>
+      <c r="K57" s="67"/>
+      <c r="L57" s="67"/>
+      <c r="M57" s="67"/>
+      <c r="N57" s="67"/>
+      <c r="O57" s="67"/>
+      <c r="P57" s="67"/>
+      <c r="Q57" s="67"/>
+      <c r="R57" s="67"/>
+      <c r="S57" s="67"/>
+      <c r="T57" s="67"/>
+      <c r="U57" s="67"/>
+      <c r="V57" s="67"/>
+      <c r="W57" s="67"/>
+      <c r="X57" s="67"/>
+      <c r="Y57" s="67"/>
+      <c r="Z57" s="67"/>
+      <c r="AA57" s="67"/>
+      <c r="AB57" s="67"/>
+      <c r="AC57" s="67"/>
+      <c r="AD57" s="67"/>
+      <c r="AE57" s="67"/>
+      <c r="AF57" s="67"/>
+      <c r="AG57" s="67"/>
+      <c r="AH57" s="67"/>
+      <c r="AI57" s="67"/>
+      <c r="AJ57" s="67"/>
+      <c r="AK57" s="67"/>
+      <c r="AL57" s="67"/>
+      <c r="AM57" s="67"/>
+      <c r="AN57" s="67"/>
+      <c r="AO57" s="67"/>
+      <c r="AP57" s="67"/>
+      <c r="AQ57" s="67"/>
+      <c r="AR57" s="67"/>
+      <c r="AS57" s="67"/>
+      <c r="AT57" s="67"/>
+      <c r="AU57" s="67"/>
+      <c r="AV57" s="67"/>
+      <c r="AW57" s="67"/>
+      <c r="AX57" s="67"/>
+      <c r="AY57" s="67"/>
+      <c r="AZ57" s="67"/>
     </row>
     <row r="58" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="11"/>
       <c r="B58" s="11"/>
-      <c r="C58" s="64" t="s">
+      <c r="C58" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="D58" s="65"/>
-      <c r="E58" s="65"/>
-      <c r="F58" s="65"/>
-      <c r="G58" s="65"/>
-      <c r="H58" s="65"/>
-      <c r="I58" s="65"/>
-      <c r="J58" s="65"/>
-      <c r="K58" s="65"/>
-      <c r="L58" s="65"/>
-      <c r="M58" s="65"/>
-      <c r="N58" s="65"/>
-      <c r="O58" s="65"/>
-      <c r="P58" s="65"/>
-      <c r="Q58" s="65"/>
-      <c r="R58" s="65"/>
-      <c r="S58" s="65"/>
-      <c r="T58" s="65"/>
-      <c r="U58" s="65"/>
-      <c r="V58" s="65"/>
-      <c r="W58" s="65"/>
-      <c r="X58" s="65"/>
-      <c r="Y58" s="65"/>
-      <c r="Z58" s="65"/>
-      <c r="AA58" s="65"/>
-      <c r="AB58" s="65"/>
-      <c r="AC58" s="65"/>
-      <c r="AD58" s="65"/>
-      <c r="AE58" s="65"/>
-      <c r="AF58" s="65"/>
-      <c r="AG58" s="65"/>
-      <c r="AH58" s="65"/>
-      <c r="AI58" s="65"/>
-      <c r="AJ58" s="65"/>
-      <c r="AK58" s="65"/>
-      <c r="AL58" s="65"/>
-      <c r="AM58" s="65"/>
-      <c r="AN58" s="65"/>
-      <c r="AO58" s="65"/>
-      <c r="AP58" s="65"/>
-      <c r="AQ58" s="65"/>
-      <c r="AR58" s="65"/>
-      <c r="AS58" s="65"/>
-      <c r="AT58" s="65"/>
-      <c r="AU58" s="65"/>
-      <c r="AV58" s="65"/>
-      <c r="AW58" s="65"/>
-      <c r="AX58" s="65"/>
-      <c r="AY58" s="65"/>
-      <c r="AZ58" s="65"/>
+      <c r="D58" s="67"/>
+      <c r="E58" s="67"/>
+      <c r="F58" s="67"/>
+      <c r="G58" s="67"/>
+      <c r="H58" s="67"/>
+      <c r="I58" s="67"/>
+      <c r="J58" s="67"/>
+      <c r="K58" s="67"/>
+      <c r="L58" s="67"/>
+      <c r="M58" s="67"/>
+      <c r="N58" s="67"/>
+      <c r="O58" s="67"/>
+      <c r="P58" s="67"/>
+      <c r="Q58" s="67"/>
+      <c r="R58" s="67"/>
+      <c r="S58" s="67"/>
+      <c r="T58" s="67"/>
+      <c r="U58" s="67"/>
+      <c r="V58" s="67"/>
+      <c r="W58" s="67"/>
+      <c r="X58" s="67"/>
+      <c r="Y58" s="67"/>
+      <c r="Z58" s="67"/>
+      <c r="AA58" s="67"/>
+      <c r="AB58" s="67"/>
+      <c r="AC58" s="67"/>
+      <c r="AD58" s="67"/>
+      <c r="AE58" s="67"/>
+      <c r="AF58" s="67"/>
+      <c r="AG58" s="67"/>
+      <c r="AH58" s="67"/>
+      <c r="AI58" s="67"/>
+      <c r="AJ58" s="67"/>
+      <c r="AK58" s="67"/>
+      <c r="AL58" s="67"/>
+      <c r="AM58" s="67"/>
+      <c r="AN58" s="67"/>
+      <c r="AO58" s="67"/>
+      <c r="AP58" s="67"/>
+      <c r="AQ58" s="67"/>
+      <c r="AR58" s="67"/>
+      <c r="AS58" s="67"/>
+      <c r="AT58" s="67"/>
+      <c r="AU58" s="67"/>
+      <c r="AV58" s="67"/>
+      <c r="AW58" s="67"/>
+      <c r="AX58" s="67"/>
+      <c r="AY58" s="67"/>
+      <c r="AZ58" s="67"/>
     </row>
     <row r="59" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="11"/>
       <c r="B59" s="11"/>
-      <c r="C59" s="64" t="s">
+      <c r="C59" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="D59" s="65"/>
-      <c r="E59" s="65"/>
-      <c r="F59" s="65"/>
-      <c r="G59" s="65"/>
-      <c r="H59" s="65"/>
-      <c r="I59" s="65"/>
-      <c r="J59" s="65"/>
-      <c r="K59" s="65"/>
-      <c r="L59" s="65"/>
-      <c r="M59" s="65"/>
-      <c r="N59" s="65"/>
-      <c r="O59" s="65"/>
-      <c r="P59" s="65"/>
-      <c r="Q59" s="65"/>
-      <c r="R59" s="65"/>
-      <c r="S59" s="65"/>
-      <c r="T59" s="65"/>
-      <c r="U59" s="65"/>
-      <c r="V59" s="65"/>
-      <c r="W59" s="65"/>
-      <c r="X59" s="65"/>
-      <c r="Y59" s="65"/>
-      <c r="Z59" s="65"/>
-      <c r="AA59" s="65"/>
-      <c r="AB59" s="65"/>
-      <c r="AC59" s="65"/>
-      <c r="AD59" s="65"/>
-      <c r="AE59" s="65"/>
-      <c r="AF59" s="65"/>
-      <c r="AG59" s="65"/>
-      <c r="AH59" s="65"/>
-      <c r="AI59" s="65"/>
-      <c r="AJ59" s="65"/>
-      <c r="AK59" s="65"/>
-      <c r="AL59" s="65"/>
-      <c r="AM59" s="65"/>
-      <c r="AN59" s="65"/>
-      <c r="AO59" s="65"/>
-      <c r="AP59" s="65"/>
-      <c r="AQ59" s="65"/>
-      <c r="AR59" s="65"/>
-      <c r="AS59" s="65"/>
-      <c r="AT59" s="65"/>
-      <c r="AU59" s="65"/>
-      <c r="AV59" s="65"/>
-      <c r="AW59" s="65"/>
-      <c r="AX59" s="65"/>
-      <c r="AY59" s="65"/>
-      <c r="AZ59" s="65"/>
+      <c r="D59" s="67"/>
+      <c r="E59" s="67"/>
+      <c r="F59" s="67"/>
+      <c r="G59" s="67"/>
+      <c r="H59" s="67"/>
+      <c r="I59" s="67"/>
+      <c r="J59" s="67"/>
+      <c r="K59" s="67"/>
+      <c r="L59" s="67"/>
+      <c r="M59" s="67"/>
+      <c r="N59" s="67"/>
+      <c r="O59" s="67"/>
+      <c r="P59" s="67"/>
+      <c r="Q59" s="67"/>
+      <c r="R59" s="67"/>
+      <c r="S59" s="67"/>
+      <c r="T59" s="67"/>
+      <c r="U59" s="67"/>
+      <c r="V59" s="67"/>
+      <c r="W59" s="67"/>
+      <c r="X59" s="67"/>
+      <c r="Y59" s="67"/>
+      <c r="Z59" s="67"/>
+      <c r="AA59" s="67"/>
+      <c r="AB59" s="67"/>
+      <c r="AC59" s="67"/>
+      <c r="AD59" s="67"/>
+      <c r="AE59" s="67"/>
+      <c r="AF59" s="67"/>
+      <c r="AG59" s="67"/>
+      <c r="AH59" s="67"/>
+      <c r="AI59" s="67"/>
+      <c r="AJ59" s="67"/>
+      <c r="AK59" s="67"/>
+      <c r="AL59" s="67"/>
+      <c r="AM59" s="67"/>
+      <c r="AN59" s="67"/>
+      <c r="AO59" s="67"/>
+      <c r="AP59" s="67"/>
+      <c r="AQ59" s="67"/>
+      <c r="AR59" s="67"/>
+      <c r="AS59" s="67"/>
+      <c r="AT59" s="67"/>
+      <c r="AU59" s="67"/>
+      <c r="AV59" s="67"/>
+      <c r="AW59" s="67"/>
+      <c r="AX59" s="67"/>
+      <c r="AY59" s="67"/>
+      <c r="AZ59" s="67"/>
     </row>
     <row r="60" spans="1:52" s="6" customFormat="1" ht="19.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="15"/>
       <c r="B60" s="16"/>
-      <c r="C60" s="64" t="s">
+      <c r="C60" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="D60" s="65"/>
-      <c r="E60" s="65"/>
-      <c r="F60" s="65"/>
-      <c r="G60" s="65"/>
-      <c r="H60" s="65"/>
-      <c r="I60" s="65"/>
-      <c r="J60" s="65"/>
-      <c r="K60" s="65"/>
-      <c r="L60" s="65"/>
-      <c r="M60" s="65"/>
-      <c r="N60" s="65"/>
-      <c r="O60" s="65"/>
-      <c r="P60" s="65"/>
-      <c r="Q60" s="65"/>
-      <c r="R60" s="65"/>
-      <c r="S60" s="65"/>
-      <c r="T60" s="65"/>
-      <c r="U60" s="65"/>
-      <c r="V60" s="65"/>
-      <c r="W60" s="65"/>
-      <c r="X60" s="65"/>
-      <c r="Y60" s="65"/>
-      <c r="Z60" s="65"/>
-      <c r="AA60" s="65"/>
-      <c r="AB60" s="65"/>
-      <c r="AC60" s="65"/>
-      <c r="AD60" s="65"/>
-      <c r="AE60" s="65"/>
-      <c r="AF60" s="65"/>
-      <c r="AG60" s="65"/>
-      <c r="AH60" s="65"/>
-      <c r="AI60" s="65"/>
-      <c r="AJ60" s="65"/>
-      <c r="AK60" s="65"/>
-      <c r="AL60" s="65"/>
-      <c r="AM60" s="65"/>
-      <c r="AN60" s="65"/>
-      <c r="AO60" s="65"/>
-      <c r="AP60" s="65"/>
-      <c r="AQ60" s="65"/>
-      <c r="AR60" s="65"/>
-      <c r="AS60" s="65"/>
-      <c r="AT60" s="65"/>
-      <c r="AU60" s="65"/>
-      <c r="AV60" s="65"/>
-      <c r="AW60" s="65"/>
-      <c r="AX60" s="65"/>
-      <c r="AY60" s="65"/>
-      <c r="AZ60" s="67"/>
+      <c r="D60" s="67"/>
+      <c r="E60" s="67"/>
+      <c r="F60" s="67"/>
+      <c r="G60" s="67"/>
+      <c r="H60" s="67"/>
+      <c r="I60" s="67"/>
+      <c r="J60" s="67"/>
+      <c r="K60" s="67"/>
+      <c r="L60" s="67"/>
+      <c r="M60" s="67"/>
+      <c r="N60" s="67"/>
+      <c r="O60" s="67"/>
+      <c r="P60" s="67"/>
+      <c r="Q60" s="67"/>
+      <c r="R60" s="67"/>
+      <c r="S60" s="67"/>
+      <c r="T60" s="67"/>
+      <c r="U60" s="67"/>
+      <c r="V60" s="67"/>
+      <c r="W60" s="67"/>
+      <c r="X60" s="67"/>
+      <c r="Y60" s="67"/>
+      <c r="Z60" s="67"/>
+      <c r="AA60" s="67"/>
+      <c r="AB60" s="67"/>
+      <c r="AC60" s="67"/>
+      <c r="AD60" s="67"/>
+      <c r="AE60" s="67"/>
+      <c r="AF60" s="67"/>
+      <c r="AG60" s="67"/>
+      <c r="AH60" s="67"/>
+      <c r="AI60" s="67"/>
+      <c r="AJ60" s="67"/>
+      <c r="AK60" s="67"/>
+      <c r="AL60" s="67"/>
+      <c r="AM60" s="67"/>
+      <c r="AN60" s="67"/>
+      <c r="AO60" s="67"/>
+      <c r="AP60" s="67"/>
+      <c r="AQ60" s="67"/>
+      <c r="AR60" s="67"/>
+      <c r="AS60" s="67"/>
+      <c r="AT60" s="67"/>
+      <c r="AU60" s="67"/>
+      <c r="AV60" s="67"/>
+      <c r="AW60" s="67"/>
+      <c r="AX60" s="67"/>
+      <c r="AY60" s="67"/>
+      <c r="AZ60" s="69"/>
     </row>
     <row r="61" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="11"/>
       <c r="B61" s="11"/>
-      <c r="C61" s="64" t="s">
+      <c r="C61" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="D61" s="65"/>
-      <c r="E61" s="65"/>
-      <c r="F61" s="65"/>
-      <c r="G61" s="65"/>
-      <c r="H61" s="65"/>
-      <c r="I61" s="65"/>
-      <c r="J61" s="65"/>
-      <c r="K61" s="65"/>
-      <c r="L61" s="65"/>
-      <c r="M61" s="65"/>
-      <c r="N61" s="65"/>
-      <c r="O61" s="65"/>
-      <c r="P61" s="65"/>
-      <c r="Q61" s="65"/>
-      <c r="R61" s="65"/>
-      <c r="S61" s="65"/>
-      <c r="T61" s="65"/>
-      <c r="U61" s="65"/>
-      <c r="V61" s="65"/>
-      <c r="W61" s="65"/>
-      <c r="X61" s="65"/>
-      <c r="Y61" s="65"/>
-      <c r="Z61" s="65"/>
-      <c r="AA61" s="65"/>
-      <c r="AB61" s="65"/>
-      <c r="AC61" s="65"/>
-      <c r="AD61" s="65"/>
-      <c r="AE61" s="65"/>
-      <c r="AF61" s="65"/>
-      <c r="AG61" s="65"/>
-      <c r="AH61" s="65"/>
-      <c r="AI61" s="65"/>
-      <c r="AJ61" s="65"/>
-      <c r="AK61" s="65"/>
-      <c r="AL61" s="65"/>
-      <c r="AM61" s="65"/>
-      <c r="AN61" s="65"/>
-      <c r="AO61" s="65"/>
-      <c r="AP61" s="65"/>
-      <c r="AQ61" s="65"/>
-      <c r="AR61" s="65"/>
-      <c r="AS61" s="65"/>
-      <c r="AT61" s="65"/>
-      <c r="AU61" s="65"/>
-      <c r="AV61" s="65"/>
-      <c r="AW61" s="65"/>
-      <c r="AX61" s="65"/>
-      <c r="AY61" s="65"/>
-      <c r="AZ61" s="65"/>
+      <c r="D61" s="67"/>
+      <c r="E61" s="67"/>
+      <c r="F61" s="67"/>
+      <c r="G61" s="67"/>
+      <c r="H61" s="67"/>
+      <c r="I61" s="67"/>
+      <c r="J61" s="67"/>
+      <c r="K61" s="67"/>
+      <c r="L61" s="67"/>
+      <c r="M61" s="67"/>
+      <c r="N61" s="67"/>
+      <c r="O61" s="67"/>
+      <c r="P61" s="67"/>
+      <c r="Q61" s="67"/>
+      <c r="R61" s="67"/>
+      <c r="S61" s="67"/>
+      <c r="T61" s="67"/>
+      <c r="U61" s="67"/>
+      <c r="V61" s="67"/>
+      <c r="W61" s="67"/>
+      <c r="X61" s="67"/>
+      <c r="Y61" s="67"/>
+      <c r="Z61" s="67"/>
+      <c r="AA61" s="67"/>
+      <c r="AB61" s="67"/>
+      <c r="AC61" s="67"/>
+      <c r="AD61" s="67"/>
+      <c r="AE61" s="67"/>
+      <c r="AF61" s="67"/>
+      <c r="AG61" s="67"/>
+      <c r="AH61" s="67"/>
+      <c r="AI61" s="67"/>
+      <c r="AJ61" s="67"/>
+      <c r="AK61" s="67"/>
+      <c r="AL61" s="67"/>
+      <c r="AM61" s="67"/>
+      <c r="AN61" s="67"/>
+      <c r="AO61" s="67"/>
+      <c r="AP61" s="67"/>
+      <c r="AQ61" s="67"/>
+      <c r="AR61" s="67"/>
+      <c r="AS61" s="67"/>
+      <c r="AT61" s="67"/>
+      <c r="AU61" s="67"/>
+      <c r="AV61" s="67"/>
+      <c r="AW61" s="67"/>
+      <c r="AX61" s="67"/>
+      <c r="AY61" s="67"/>
+      <c r="AZ61" s="67"/>
     </row>
     <row r="62" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="11"/>
       <c r="B62" s="11"/>
-      <c r="C62" s="68" t="s">
+      <c r="C62" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="D62" s="69"/>
-      <c r="E62" s="69"/>
-      <c r="F62" s="69"/>
-      <c r="G62" s="69"/>
-      <c r="H62" s="69"/>
-      <c r="I62" s="69"/>
-      <c r="J62" s="69"/>
-      <c r="K62" s="69"/>
-      <c r="L62" s="69"/>
-      <c r="M62" s="69"/>
-      <c r="N62" s="69"/>
-      <c r="O62" s="69"/>
-      <c r="P62" s="69"/>
-      <c r="Q62" s="69"/>
-      <c r="R62" s="69"/>
-      <c r="S62" s="69"/>
-      <c r="T62" s="69"/>
-      <c r="U62" s="69"/>
-      <c r="V62" s="69"/>
-      <c r="W62" s="69"/>
-      <c r="X62" s="69"/>
-      <c r="Y62" s="69"/>
-      <c r="Z62" s="69"/>
-      <c r="AA62" s="69"/>
-      <c r="AB62" s="69"/>
-      <c r="AC62" s="69"/>
-      <c r="AD62" s="69"/>
-      <c r="AE62" s="69"/>
-      <c r="AF62" s="69"/>
-      <c r="AG62" s="69"/>
-      <c r="AH62" s="69"/>
-      <c r="AI62" s="69"/>
-      <c r="AJ62" s="69"/>
-      <c r="AK62" s="69"/>
-      <c r="AL62" s="69"/>
-      <c r="AM62" s="69"/>
-      <c r="AN62" s="69"/>
-      <c r="AO62" s="69"/>
-      <c r="AP62" s="69"/>
-      <c r="AQ62" s="69"/>
-      <c r="AR62" s="69"/>
-      <c r="AS62" s="69"/>
-      <c r="AT62" s="69"/>
-      <c r="AU62" s="69"/>
-      <c r="AV62" s="69"/>
-      <c r="AW62" s="69"/>
-      <c r="AX62" s="69"/>
-      <c r="AY62" s="69"/>
-      <c r="AZ62" s="69"/>
+      <c r="D62" s="71"/>
+      <c r="E62" s="71"/>
+      <c r="F62" s="71"/>
+      <c r="G62" s="71"/>
+      <c r="H62" s="71"/>
+      <c r="I62" s="71"/>
+      <c r="J62" s="71"/>
+      <c r="K62" s="71"/>
+      <c r="L62" s="71"/>
+      <c r="M62" s="71"/>
+      <c r="N62" s="71"/>
+      <c r="O62" s="71"/>
+      <c r="P62" s="71"/>
+      <c r="Q62" s="71"/>
+      <c r="R62" s="71"/>
+      <c r="S62" s="71"/>
+      <c r="T62" s="71"/>
+      <c r="U62" s="71"/>
+      <c r="V62" s="71"/>
+      <c r="W62" s="71"/>
+      <c r="X62" s="71"/>
+      <c r="Y62" s="71"/>
+      <c r="Z62" s="71"/>
+      <c r="AA62" s="71"/>
+      <c r="AB62" s="71"/>
+      <c r="AC62" s="71"/>
+      <c r="AD62" s="71"/>
+      <c r="AE62" s="71"/>
+      <c r="AF62" s="71"/>
+      <c r="AG62" s="71"/>
+      <c r="AH62" s="71"/>
+      <c r="AI62" s="71"/>
+      <c r="AJ62" s="71"/>
+      <c r="AK62" s="71"/>
+      <c r="AL62" s="71"/>
+      <c r="AM62" s="71"/>
+      <c r="AN62" s="71"/>
+      <c r="AO62" s="71"/>
+      <c r="AP62" s="71"/>
+      <c r="AQ62" s="71"/>
+      <c r="AR62" s="71"/>
+      <c r="AS62" s="71"/>
+      <c r="AT62" s="71"/>
+      <c r="AU62" s="71"/>
+      <c r="AV62" s="71"/>
+      <c r="AW62" s="71"/>
+      <c r="AX62" s="71"/>
+      <c r="AY62" s="71"/>
+      <c r="AZ62" s="71"/>
     </row>
     <row r="63" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="11"/>
       <c r="B63" s="11"/>
-      <c r="C63" s="64" t="s">
+      <c r="C63" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="D63" s="65"/>
-      <c r="E63" s="65"/>
-      <c r="F63" s="65"/>
-      <c r="G63" s="65"/>
-      <c r="H63" s="65"/>
-      <c r="I63" s="65"/>
-      <c r="J63" s="65"/>
-      <c r="K63" s="65"/>
-      <c r="L63" s="65"/>
-      <c r="M63" s="65"/>
-      <c r="N63" s="65"/>
-      <c r="O63" s="65"/>
-      <c r="P63" s="65"/>
-      <c r="Q63" s="65"/>
-      <c r="R63" s="65"/>
-      <c r="S63" s="65"/>
-      <c r="T63" s="65"/>
-      <c r="U63" s="65"/>
-      <c r="V63" s="65"/>
-      <c r="W63" s="65"/>
-      <c r="X63" s="65"/>
-      <c r="Y63" s="65"/>
-      <c r="Z63" s="65"/>
-      <c r="AA63" s="65"/>
-      <c r="AB63" s="65"/>
-      <c r="AC63" s="65"/>
-      <c r="AD63" s="65"/>
-      <c r="AE63" s="65"/>
-      <c r="AF63" s="65"/>
-      <c r="AG63" s="65"/>
-      <c r="AH63" s="65"/>
-      <c r="AI63" s="65"/>
-      <c r="AJ63" s="65"/>
-      <c r="AK63" s="65"/>
-      <c r="AL63" s="65"/>
-      <c r="AM63" s="65"/>
-      <c r="AN63" s="65"/>
-      <c r="AO63" s="65"/>
-      <c r="AP63" s="65"/>
-      <c r="AQ63" s="65"/>
-      <c r="AR63" s="65"/>
-      <c r="AS63" s="65"/>
-      <c r="AT63" s="65"/>
-      <c r="AU63" s="65"/>
-      <c r="AV63" s="65"/>
-      <c r="AW63" s="65"/>
-      <c r="AX63" s="65"/>
-      <c r="AY63" s="65"/>
-      <c r="AZ63" s="65"/>
+      <c r="D63" s="67"/>
+      <c r="E63" s="67"/>
+      <c r="F63" s="67"/>
+      <c r="G63" s="67"/>
+      <c r="H63" s="67"/>
+      <c r="I63" s="67"/>
+      <c r="J63" s="67"/>
+      <c r="K63" s="67"/>
+      <c r="L63" s="67"/>
+      <c r="M63" s="67"/>
+      <c r="N63" s="67"/>
+      <c r="O63" s="67"/>
+      <c r="P63" s="67"/>
+      <c r="Q63" s="67"/>
+      <c r="R63" s="67"/>
+      <c r="S63" s="67"/>
+      <c r="T63" s="67"/>
+      <c r="U63" s="67"/>
+      <c r="V63" s="67"/>
+      <c r="W63" s="67"/>
+      <c r="X63" s="67"/>
+      <c r="Y63" s="67"/>
+      <c r="Z63" s="67"/>
+      <c r="AA63" s="67"/>
+      <c r="AB63" s="67"/>
+      <c r="AC63" s="67"/>
+      <c r="AD63" s="67"/>
+      <c r="AE63" s="67"/>
+      <c r="AF63" s="67"/>
+      <c r="AG63" s="67"/>
+      <c r="AH63" s="67"/>
+      <c r="AI63" s="67"/>
+      <c r="AJ63" s="67"/>
+      <c r="AK63" s="67"/>
+      <c r="AL63" s="67"/>
+      <c r="AM63" s="67"/>
+      <c r="AN63" s="67"/>
+      <c r="AO63" s="67"/>
+      <c r="AP63" s="67"/>
+      <c r="AQ63" s="67"/>
+      <c r="AR63" s="67"/>
+      <c r="AS63" s="67"/>
+      <c r="AT63" s="67"/>
+      <c r="AU63" s="67"/>
+      <c r="AV63" s="67"/>
+      <c r="AW63" s="67"/>
+      <c r="AX63" s="67"/>
+      <c r="AY63" s="67"/>
+      <c r="AZ63" s="67"/>
     </row>
     <row r="64" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="11"/>
       <c r="B64" s="11"/>
-      <c r="C64" s="68" t="s">
+      <c r="C64" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="D64" s="69"/>
-      <c r="E64" s="69"/>
-      <c r="F64" s="69"/>
-      <c r="G64" s="69"/>
-      <c r="H64" s="69"/>
-      <c r="I64" s="69"/>
-      <c r="J64" s="69"/>
-      <c r="K64" s="69"/>
-      <c r="L64" s="69"/>
-      <c r="M64" s="69"/>
-      <c r="N64" s="69"/>
-      <c r="O64" s="69"/>
-      <c r="P64" s="69"/>
-      <c r="Q64" s="69"/>
-      <c r="R64" s="69"/>
-      <c r="S64" s="69"/>
-      <c r="T64" s="69"/>
-      <c r="U64" s="69"/>
-      <c r="V64" s="69"/>
-      <c r="W64" s="69"/>
-      <c r="X64" s="69"/>
-      <c r="Y64" s="69"/>
-      <c r="Z64" s="69"/>
-      <c r="AA64" s="69"/>
-      <c r="AB64" s="69"/>
-      <c r="AC64" s="69"/>
-      <c r="AD64" s="69"/>
-      <c r="AE64" s="69"/>
-      <c r="AF64" s="69"/>
-      <c r="AG64" s="69"/>
-      <c r="AH64" s="69"/>
-      <c r="AI64" s="69"/>
-      <c r="AJ64" s="69"/>
-      <c r="AK64" s="69"/>
-      <c r="AL64" s="69"/>
-      <c r="AM64" s="69"/>
-      <c r="AN64" s="69"/>
-      <c r="AO64" s="69"/>
-      <c r="AP64" s="69"/>
-      <c r="AQ64" s="69"/>
-      <c r="AR64" s="69"/>
-      <c r="AS64" s="69"/>
-      <c r="AT64" s="69"/>
-      <c r="AU64" s="69"/>
-      <c r="AV64" s="69"/>
-      <c r="AW64" s="69"/>
-      <c r="AX64" s="69"/>
-      <c r="AY64" s="69"/>
-      <c r="AZ64" s="69"/>
+      <c r="D64" s="71"/>
+      <c r="E64" s="71"/>
+      <c r="F64" s="71"/>
+      <c r="G64" s="71"/>
+      <c r="H64" s="71"/>
+      <c r="I64" s="71"/>
+      <c r="J64" s="71"/>
+      <c r="K64" s="71"/>
+      <c r="L64" s="71"/>
+      <c r="M64" s="71"/>
+      <c r="N64" s="71"/>
+      <c r="O64" s="71"/>
+      <c r="P64" s="71"/>
+      <c r="Q64" s="71"/>
+      <c r="R64" s="71"/>
+      <c r="S64" s="71"/>
+      <c r="T64" s="71"/>
+      <c r="U64" s="71"/>
+      <c r="V64" s="71"/>
+      <c r="W64" s="71"/>
+      <c r="X64" s="71"/>
+      <c r="Y64" s="71"/>
+      <c r="Z64" s="71"/>
+      <c r="AA64" s="71"/>
+      <c r="AB64" s="71"/>
+      <c r="AC64" s="71"/>
+      <c r="AD64" s="71"/>
+      <c r="AE64" s="71"/>
+      <c r="AF64" s="71"/>
+      <c r="AG64" s="71"/>
+      <c r="AH64" s="71"/>
+      <c r="AI64" s="71"/>
+      <c r="AJ64" s="71"/>
+      <c r="AK64" s="71"/>
+      <c r="AL64" s="71"/>
+      <c r="AM64" s="71"/>
+      <c r="AN64" s="71"/>
+      <c r="AO64" s="71"/>
+      <c r="AP64" s="71"/>
+      <c r="AQ64" s="71"/>
+      <c r="AR64" s="71"/>
+      <c r="AS64" s="71"/>
+      <c r="AT64" s="71"/>
+      <c r="AU64" s="71"/>
+      <c r="AV64" s="71"/>
+      <c r="AW64" s="71"/>
+      <c r="AX64" s="71"/>
+      <c r="AY64" s="71"/>
+      <c r="AZ64" s="71"/>
     </row>
     <row r="65" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="11"/>
@@ -12446,55 +12446,55 @@
       </c>
       <c r="B66" s="27"/>
       <c r="C66" s="66"/>
-      <c r="D66" s="65"/>
-      <c r="E66" s="65"/>
-      <c r="F66" s="65"/>
-      <c r="G66" s="65"/>
-      <c r="H66" s="65"/>
-      <c r="I66" s="65"/>
-      <c r="J66" s="65"/>
-      <c r="K66" s="65"/>
-      <c r="L66" s="65"/>
-      <c r="M66" s="65"/>
-      <c r="N66" s="65"/>
-      <c r="O66" s="65"/>
-      <c r="P66" s="65"/>
-      <c r="Q66" s="65"/>
-      <c r="R66" s="65"/>
-      <c r="S66" s="65"/>
-      <c r="T66" s="65"/>
-      <c r="U66" s="65"/>
-      <c r="V66" s="65"/>
-      <c r="W66" s="65"/>
-      <c r="X66" s="65"/>
-      <c r="Y66" s="65"/>
-      <c r="Z66" s="65"/>
-      <c r="AA66" s="65"/>
-      <c r="AB66" s="65"/>
-      <c r="AC66" s="65"/>
-      <c r="AD66" s="65"/>
-      <c r="AE66" s="65"/>
-      <c r="AF66" s="65"/>
-      <c r="AG66" s="65"/>
-      <c r="AH66" s="65"/>
-      <c r="AI66" s="65"/>
-      <c r="AJ66" s="65"/>
-      <c r="AK66" s="65"/>
-      <c r="AL66" s="65"/>
-      <c r="AM66" s="65"/>
-      <c r="AN66" s="65"/>
-      <c r="AO66" s="65"/>
-      <c r="AP66" s="65"/>
-      <c r="AQ66" s="65"/>
-      <c r="AR66" s="65"/>
-      <c r="AS66" s="65"/>
-      <c r="AT66" s="65"/>
-      <c r="AU66" s="65"/>
-      <c r="AV66" s="65"/>
-      <c r="AW66" s="65"/>
-      <c r="AX66" s="65"/>
-      <c r="AY66" s="65"/>
-      <c r="AZ66" s="65"/>
+      <c r="D66" s="67"/>
+      <c r="E66" s="67"/>
+      <c r="F66" s="67"/>
+      <c r="G66" s="67"/>
+      <c r="H66" s="67"/>
+      <c r="I66" s="67"/>
+      <c r="J66" s="67"/>
+      <c r="K66" s="67"/>
+      <c r="L66" s="67"/>
+      <c r="M66" s="67"/>
+      <c r="N66" s="67"/>
+      <c r="O66" s="67"/>
+      <c r="P66" s="67"/>
+      <c r="Q66" s="67"/>
+      <c r="R66" s="67"/>
+      <c r="S66" s="67"/>
+      <c r="T66" s="67"/>
+      <c r="U66" s="67"/>
+      <c r="V66" s="67"/>
+      <c r="W66" s="67"/>
+      <c r="X66" s="67"/>
+      <c r="Y66" s="67"/>
+      <c r="Z66" s="67"/>
+      <c r="AA66" s="67"/>
+      <c r="AB66" s="67"/>
+      <c r="AC66" s="67"/>
+      <c r="AD66" s="67"/>
+      <c r="AE66" s="67"/>
+      <c r="AF66" s="67"/>
+      <c r="AG66" s="67"/>
+      <c r="AH66" s="67"/>
+      <c r="AI66" s="67"/>
+      <c r="AJ66" s="67"/>
+      <c r="AK66" s="67"/>
+      <c r="AL66" s="67"/>
+      <c r="AM66" s="67"/>
+      <c r="AN66" s="67"/>
+      <c r="AO66" s="67"/>
+      <c r="AP66" s="67"/>
+      <c r="AQ66" s="67"/>
+      <c r="AR66" s="67"/>
+      <c r="AS66" s="67"/>
+      <c r="AT66" s="67"/>
+      <c r="AU66" s="67"/>
+      <c r="AV66" s="67"/>
+      <c r="AW66" s="67"/>
+      <c r="AX66" s="67"/>
+      <c r="AY66" s="67"/>
+      <c r="AZ66" s="67"/>
     </row>
     <row r="67" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="12"/>
@@ -12502,55 +12502,55 @@
       <c r="C67" s="66" t="s">
         <v>118</v>
       </c>
-      <c r="D67" s="65"/>
-      <c r="E67" s="65"/>
-      <c r="F67" s="65"/>
-      <c r="G67" s="65"/>
-      <c r="H67" s="65"/>
-      <c r="I67" s="65"/>
-      <c r="J67" s="65"/>
-      <c r="K67" s="65"/>
-      <c r="L67" s="65"/>
-      <c r="M67" s="65"/>
-      <c r="N67" s="65"/>
-      <c r="O67" s="65"/>
-      <c r="P67" s="65"/>
-      <c r="Q67" s="65"/>
-      <c r="R67" s="65"/>
-      <c r="S67" s="65"/>
-      <c r="T67" s="65"/>
-      <c r="U67" s="65"/>
-      <c r="V67" s="65"/>
-      <c r="W67" s="65"/>
-      <c r="X67" s="65"/>
-      <c r="Y67" s="65"/>
-      <c r="Z67" s="65"/>
-      <c r="AA67" s="65"/>
-      <c r="AB67" s="65"/>
-      <c r="AC67" s="65"/>
-      <c r="AD67" s="65"/>
-      <c r="AE67" s="65"/>
-      <c r="AF67" s="65"/>
-      <c r="AG67" s="65"/>
-      <c r="AH67" s="65"/>
-      <c r="AI67" s="65"/>
-      <c r="AJ67" s="65"/>
-      <c r="AK67" s="65"/>
-      <c r="AL67" s="65"/>
-      <c r="AM67" s="65"/>
-      <c r="AN67" s="65"/>
-      <c r="AO67" s="65"/>
-      <c r="AP67" s="65"/>
-      <c r="AQ67" s="65"/>
-      <c r="AR67" s="65"/>
-      <c r="AS67" s="65"/>
-      <c r="AT67" s="65"/>
-      <c r="AU67" s="65"/>
-      <c r="AV67" s="65"/>
-      <c r="AW67" s="65"/>
-      <c r="AX67" s="65"/>
-      <c r="AY67" s="65"/>
-      <c r="AZ67" s="65"/>
+      <c r="D67" s="67"/>
+      <c r="E67" s="67"/>
+      <c r="F67" s="67"/>
+      <c r="G67" s="67"/>
+      <c r="H67" s="67"/>
+      <c r="I67" s="67"/>
+      <c r="J67" s="67"/>
+      <c r="K67" s="67"/>
+      <c r="L67" s="67"/>
+      <c r="M67" s="67"/>
+      <c r="N67" s="67"/>
+      <c r="O67" s="67"/>
+      <c r="P67" s="67"/>
+      <c r="Q67" s="67"/>
+      <c r="R67" s="67"/>
+      <c r="S67" s="67"/>
+      <c r="T67" s="67"/>
+      <c r="U67" s="67"/>
+      <c r="V67" s="67"/>
+      <c r="W67" s="67"/>
+      <c r="X67" s="67"/>
+      <c r="Y67" s="67"/>
+      <c r="Z67" s="67"/>
+      <c r="AA67" s="67"/>
+      <c r="AB67" s="67"/>
+      <c r="AC67" s="67"/>
+      <c r="AD67" s="67"/>
+      <c r="AE67" s="67"/>
+      <c r="AF67" s="67"/>
+      <c r="AG67" s="67"/>
+      <c r="AH67" s="67"/>
+      <c r="AI67" s="67"/>
+      <c r="AJ67" s="67"/>
+      <c r="AK67" s="67"/>
+      <c r="AL67" s="67"/>
+      <c r="AM67" s="67"/>
+      <c r="AN67" s="67"/>
+      <c r="AO67" s="67"/>
+      <c r="AP67" s="67"/>
+      <c r="AQ67" s="67"/>
+      <c r="AR67" s="67"/>
+      <c r="AS67" s="67"/>
+      <c r="AT67" s="67"/>
+      <c r="AU67" s="67"/>
+      <c r="AV67" s="67"/>
+      <c r="AW67" s="67"/>
+      <c r="AX67" s="67"/>
+      <c r="AY67" s="67"/>
+      <c r="AZ67" s="67"/>
     </row>
     <row r="68" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="12"/>
@@ -12558,55 +12558,55 @@
       <c r="C68" s="66" t="s">
         <v>119</v>
       </c>
-      <c r="D68" s="65"/>
-      <c r="E68" s="65"/>
-      <c r="F68" s="65"/>
-      <c r="G68" s="65"/>
-      <c r="H68" s="65"/>
-      <c r="I68" s="65"/>
-      <c r="J68" s="65"/>
-      <c r="K68" s="65"/>
-      <c r="L68" s="65"/>
-      <c r="M68" s="65"/>
-      <c r="N68" s="65"/>
-      <c r="O68" s="65"/>
-      <c r="P68" s="65"/>
-      <c r="Q68" s="65"/>
-      <c r="R68" s="65"/>
-      <c r="S68" s="65"/>
-      <c r="T68" s="65"/>
-      <c r="U68" s="65"/>
-      <c r="V68" s="65"/>
-      <c r="W68" s="65"/>
-      <c r="X68" s="65"/>
-      <c r="Y68" s="65"/>
-      <c r="Z68" s="65"/>
-      <c r="AA68" s="65"/>
-      <c r="AB68" s="65"/>
-      <c r="AC68" s="65"/>
-      <c r="AD68" s="65"/>
-      <c r="AE68" s="65"/>
-      <c r="AF68" s="65"/>
-      <c r="AG68" s="65"/>
-      <c r="AH68" s="65"/>
-      <c r="AI68" s="65"/>
-      <c r="AJ68" s="65"/>
-      <c r="AK68" s="65"/>
-      <c r="AL68" s="65"/>
-      <c r="AM68" s="65"/>
-      <c r="AN68" s="65"/>
-      <c r="AO68" s="65"/>
-      <c r="AP68" s="65"/>
-      <c r="AQ68" s="65"/>
-      <c r="AR68" s="65"/>
-      <c r="AS68" s="65"/>
-      <c r="AT68" s="65"/>
-      <c r="AU68" s="65"/>
-      <c r="AV68" s="65"/>
-      <c r="AW68" s="65"/>
-      <c r="AX68" s="65"/>
-      <c r="AY68" s="65"/>
-      <c r="AZ68" s="65"/>
+      <c r="D68" s="67"/>
+      <c r="E68" s="67"/>
+      <c r="F68" s="67"/>
+      <c r="G68" s="67"/>
+      <c r="H68" s="67"/>
+      <c r="I68" s="67"/>
+      <c r="J68" s="67"/>
+      <c r="K68" s="67"/>
+      <c r="L68" s="67"/>
+      <c r="M68" s="67"/>
+      <c r="N68" s="67"/>
+      <c r="O68" s="67"/>
+      <c r="P68" s="67"/>
+      <c r="Q68" s="67"/>
+      <c r="R68" s="67"/>
+      <c r="S68" s="67"/>
+      <c r="T68" s="67"/>
+      <c r="U68" s="67"/>
+      <c r="V68" s="67"/>
+      <c r="W68" s="67"/>
+      <c r="X68" s="67"/>
+      <c r="Y68" s="67"/>
+      <c r="Z68" s="67"/>
+      <c r="AA68" s="67"/>
+      <c r="AB68" s="67"/>
+      <c r="AC68" s="67"/>
+      <c r="AD68" s="67"/>
+      <c r="AE68" s="67"/>
+      <c r="AF68" s="67"/>
+      <c r="AG68" s="67"/>
+      <c r="AH68" s="67"/>
+      <c r="AI68" s="67"/>
+      <c r="AJ68" s="67"/>
+      <c r="AK68" s="67"/>
+      <c r="AL68" s="67"/>
+      <c r="AM68" s="67"/>
+      <c r="AN68" s="67"/>
+      <c r="AO68" s="67"/>
+      <c r="AP68" s="67"/>
+      <c r="AQ68" s="67"/>
+      <c r="AR68" s="67"/>
+      <c r="AS68" s="67"/>
+      <c r="AT68" s="67"/>
+      <c r="AU68" s="67"/>
+      <c r="AV68" s="67"/>
+      <c r="AW68" s="67"/>
+      <c r="AX68" s="67"/>
+      <c r="AY68" s="67"/>
+      <c r="AZ68" s="67"/>
     </row>
     <row r="69" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="12"/>
@@ -12614,55 +12614,55 @@
       <c r="C69" s="66" t="s">
         <v>120</v>
       </c>
-      <c r="D69" s="65"/>
-      <c r="E69" s="65"/>
-      <c r="F69" s="65"/>
-      <c r="G69" s="65"/>
-      <c r="H69" s="65"/>
-      <c r="I69" s="65"/>
-      <c r="J69" s="65"/>
-      <c r="K69" s="65"/>
-      <c r="L69" s="65"/>
-      <c r="M69" s="65"/>
-      <c r="N69" s="65"/>
-      <c r="O69" s="65"/>
-      <c r="P69" s="65"/>
-      <c r="Q69" s="65"/>
-      <c r="R69" s="65"/>
-      <c r="S69" s="65"/>
-      <c r="T69" s="65"/>
-      <c r="U69" s="65"/>
-      <c r="V69" s="65"/>
-      <c r="W69" s="65"/>
-      <c r="X69" s="65"/>
-      <c r="Y69" s="65"/>
-      <c r="Z69" s="65"/>
-      <c r="AA69" s="65"/>
-      <c r="AB69" s="65"/>
-      <c r="AC69" s="65"/>
-      <c r="AD69" s="65"/>
-      <c r="AE69" s="65"/>
-      <c r="AF69" s="65"/>
-      <c r="AG69" s="65"/>
-      <c r="AH69" s="65"/>
-      <c r="AI69" s="65"/>
-      <c r="AJ69" s="65"/>
-      <c r="AK69" s="65"/>
-      <c r="AL69" s="65"/>
-      <c r="AM69" s="65"/>
-      <c r="AN69" s="65"/>
-      <c r="AO69" s="65"/>
-      <c r="AP69" s="65"/>
-      <c r="AQ69" s="65"/>
-      <c r="AR69" s="65"/>
-      <c r="AS69" s="65"/>
-      <c r="AT69" s="65"/>
-      <c r="AU69" s="65"/>
-      <c r="AV69" s="65"/>
-      <c r="AW69" s="65"/>
-      <c r="AX69" s="65"/>
-      <c r="AY69" s="65"/>
-      <c r="AZ69" s="65"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="67"/>
+      <c r="F69" s="67"/>
+      <c r="G69" s="67"/>
+      <c r="H69" s="67"/>
+      <c r="I69" s="67"/>
+      <c r="J69" s="67"/>
+      <c r="K69" s="67"/>
+      <c r="L69" s="67"/>
+      <c r="M69" s="67"/>
+      <c r="N69" s="67"/>
+      <c r="O69" s="67"/>
+      <c r="P69" s="67"/>
+      <c r="Q69" s="67"/>
+      <c r="R69" s="67"/>
+      <c r="S69" s="67"/>
+      <c r="T69" s="67"/>
+      <c r="U69" s="67"/>
+      <c r="V69" s="67"/>
+      <c r="W69" s="67"/>
+      <c r="X69" s="67"/>
+      <c r="Y69" s="67"/>
+      <c r="Z69" s="67"/>
+      <c r="AA69" s="67"/>
+      <c r="AB69" s="67"/>
+      <c r="AC69" s="67"/>
+      <c r="AD69" s="67"/>
+      <c r="AE69" s="67"/>
+      <c r="AF69" s="67"/>
+      <c r="AG69" s="67"/>
+      <c r="AH69" s="67"/>
+      <c r="AI69" s="67"/>
+      <c r="AJ69" s="67"/>
+      <c r="AK69" s="67"/>
+      <c r="AL69" s="67"/>
+      <c r="AM69" s="67"/>
+      <c r="AN69" s="67"/>
+      <c r="AO69" s="67"/>
+      <c r="AP69" s="67"/>
+      <c r="AQ69" s="67"/>
+      <c r="AR69" s="67"/>
+      <c r="AS69" s="67"/>
+      <c r="AT69" s="67"/>
+      <c r="AU69" s="67"/>
+      <c r="AV69" s="67"/>
+      <c r="AW69" s="67"/>
+      <c r="AX69" s="67"/>
+      <c r="AY69" s="67"/>
+      <c r="AZ69" s="67"/>
     </row>
     <row r="70" spans="1:52" ht="19.05" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="12"/>
@@ -12670,55 +12670,55 @@
       <c r="C70" s="66" t="s">
         <v>121</v>
       </c>
-      <c r="D70" s="65"/>
-      <c r="E70" s="65"/>
-      <c r="F70" s="65"/>
-      <c r="G70" s="65"/>
-      <c r="H70" s="65"/>
-      <c r="I70" s="65"/>
-      <c r="J70" s="65"/>
-      <c r="K70" s="65"/>
-      <c r="L70" s="65"/>
-      <c r="M70" s="65"/>
-      <c r="N70" s="65"/>
-      <c r="O70" s="65"/>
-      <c r="P70" s="65"/>
-      <c r="Q70" s="65"/>
-      <c r="R70" s="65"/>
-      <c r="S70" s="65"/>
-      <c r="T70" s="65"/>
-      <c r="U70" s="65"/>
-      <c r="V70" s="65"/>
-      <c r="W70" s="65"/>
-      <c r="X70" s="65"/>
-      <c r="Y70" s="65"/>
-      <c r="Z70" s="65"/>
-      <c r="AA70" s="65"/>
-      <c r="AB70" s="65"/>
-      <c r="AC70" s="65"/>
-      <c r="AD70" s="65"/>
-      <c r="AE70" s="65"/>
-      <c r="AF70" s="65"/>
-      <c r="AG70" s="65"/>
-      <c r="AH70" s="65"/>
-      <c r="AI70" s="65"/>
-      <c r="AJ70" s="65"/>
-      <c r="AK70" s="65"/>
-      <c r="AL70" s="65"/>
-      <c r="AM70" s="65"/>
-      <c r="AN70" s="65"/>
-      <c r="AO70" s="65"/>
-      <c r="AP70" s="65"/>
-      <c r="AQ70" s="65"/>
-      <c r="AR70" s="65"/>
-      <c r="AS70" s="65"/>
-      <c r="AT70" s="65"/>
-      <c r="AU70" s="65"/>
-      <c r="AV70" s="65"/>
-      <c r="AW70" s="65"/>
-      <c r="AX70" s="65"/>
-      <c r="AY70" s="65"/>
-      <c r="AZ70" s="65"/>
+      <c r="D70" s="67"/>
+      <c r="E70" s="67"/>
+      <c r="F70" s="67"/>
+      <c r="G70" s="67"/>
+      <c r="H70" s="67"/>
+      <c r="I70" s="67"/>
+      <c r="J70" s="67"/>
+      <c r="K70" s="67"/>
+      <c r="L70" s="67"/>
+      <c r="M70" s="67"/>
+      <c r="N70" s="67"/>
+      <c r="O70" s="67"/>
+      <c r="P70" s="67"/>
+      <c r="Q70" s="67"/>
+      <c r="R70" s="67"/>
+      <c r="S70" s="67"/>
+      <c r="T70" s="67"/>
+      <c r="U70" s="67"/>
+      <c r="V70" s="67"/>
+      <c r="W70" s="67"/>
+      <c r="X70" s="67"/>
+      <c r="Y70" s="67"/>
+      <c r="Z70" s="67"/>
+      <c r="AA70" s="67"/>
+      <c r="AB70" s="67"/>
+      <c r="AC70" s="67"/>
+      <c r="AD70" s="67"/>
+      <c r="AE70" s="67"/>
+      <c r="AF70" s="67"/>
+      <c r="AG70" s="67"/>
+      <c r="AH70" s="67"/>
+      <c r="AI70" s="67"/>
+      <c r="AJ70" s="67"/>
+      <c r="AK70" s="67"/>
+      <c r="AL70" s="67"/>
+      <c r="AM70" s="67"/>
+      <c r="AN70" s="67"/>
+      <c r="AO70" s="67"/>
+      <c r="AP70" s="67"/>
+      <c r="AQ70" s="67"/>
+      <c r="AR70" s="67"/>
+      <c r="AS70" s="67"/>
+      <c r="AT70" s="67"/>
+      <c r="AU70" s="67"/>
+      <c r="AV70" s="67"/>
+      <c r="AW70" s="67"/>
+      <c r="AX70" s="67"/>
+      <c r="AY70" s="67"/>
+      <c r="AZ70" s="67"/>
     </row>
     <row r="71" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="12"/>
